--- a/ai_service/sample_dataset.xlsx
+++ b/ai_service/sample_dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\82102\Desktop\RAG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{955764B6-0DA6-44F6-9005-8EBACC9CD7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558068BA-2FAA-430C-8B92-03861456620B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1470" windowWidth="12735" windowHeight="9308" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2287" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2645" uniqueCount="928">
   <si>
     <t>paper_id</t>
   </si>
@@ -2931,12 +2931,979 @@
   <si>
     <t>질병 위험; 수면장애</t>
   </si>
+  <si>
+    <t>Wong_2021</t>
+  </si>
+  <si>
+    <t>Defining skin aging and its risk factors</t>
+  </si>
+  <si>
+    <t>s01</t>
+  </si>
+  <si>
+    <t>Results and discussion</t>
+  </si>
+  <si>
+    <t>Non-modifiable risk factors (intrinsic aging)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Associations with age were obtained for eight skin aging phenotypes... Significant associations were found for wrinkling (pOR 3.96, 95% CI 1.75, 8.96). </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>intrinsic_aging</t>
+  </si>
+  <si>
+    <t>주름 중증도</t>
+  </si>
+  <si>
+    <t>adult, older_adult</t>
+  </si>
+  <si>
+    <t>성인 및 노인</t>
+  </si>
+  <si>
+    <t>systematic_review_meta_analysis</t>
+  </si>
+  <si>
+    <t>POR</t>
+  </si>
+  <si>
+    <t>ratio</t>
+  </si>
+  <si>
+    <t>c01</t>
+  </si>
+  <si>
+    <r>
+      <t>Population:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 전 연령대 인간 (18-101세) </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Exposure/Condition:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 연령 증가 (Age as a continuous variable)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Comparator:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 연령대 간 비교</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Outcome:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> wrinkle_severity (주름 중증도)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Result:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 연령이 증가할수록 주름 발생 위험이 약 3.96배 유의미하게 증가함 </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>33</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Stats:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> pOR=3.96, 95% CI [1.75, 8.96], p&lt;0.05 </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Design:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 메타분석 (랜덤 효과 모델) </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <t>&lt;0.05</t>
+  </si>
+  <si>
+    <t>p01</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">나이가 들수록 피부 주름이 형성될 확률이 매우 높아집니다. 연구 결과, 연령 증가는 주름 발생 위험을 약 4배 가까이 높이는 가장 강력한 내적 요인으로 확인되었습니다. </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>6666</t>
+    </r>
+  </si>
+  <si>
+    <t>s02</t>
+  </si>
+  <si>
+    <t>Modifiable factors (extrinsic aging) - Smoking</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Finally, a significant association found for wrinkling and current smoking (pOR 3.21, 95% CI 1.56, 6.58)... Nonetheless, there was a dose-response relationship between pack-years of smoking and wrinkling. </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>7777</t>
+    </r>
+  </si>
+  <si>
+    <t>extrinsic_aging</t>
+  </si>
+  <si>
+    <t>male, female</t>
+  </si>
+  <si>
+    <t>성인 남녀</t>
+  </si>
+  <si>
+    <t>c02</t>
+  </si>
+  <si>
+    <r>
+      <t>Population:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 현재 흡연자 및 비흡연자 </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Exposure/Condition:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 현재 흡연 상태 (Current smoking)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Comparator:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 비흡연자 (Never smokers)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Result:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 현재 흡연자는 비흡연자에 비해 주름 발생 위험이 3.21배 높으며, 흡연량(pack-years)에 비례하여 악화됨 </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>9999</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Stats:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> pOR=3.21, 95% CI [1.56, 6.58] </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1010</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Design:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 메타분석 (관찰 연구 기반) </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>111111</t>
+    </r>
+  </si>
+  <si>
+    <t>p02</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">흡연은 피부 주름을 심화시키는 주요 외부 요인입니다. 현재 담배를 피우는 사람은 그렇지 않은 사람보다 주름이 생길 확률이 3배 이상 높으며, 흡연 기간과 양이 늘어날수록 주름은 더 깊어집니다. </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>12121212</t>
+    </r>
+  </si>
+  <si>
+    <t>s03</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A related protective factor, sunscreen use, was significantly associated with wrinkling (pOR 0.50, 95% CI 0.25, 0.98) with non-significant heterogeneity ($I^2=0.00\%$, p=0.387). </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>13</t>
+    </r>
+  </si>
+  <si>
+    <t>adult</t>
+  </si>
+  <si>
+    <t>성인</t>
+  </si>
+  <si>
+    <t>protective</t>
+  </si>
+  <si>
+    <t>c03</t>
+  </si>
+  <si>
+    <r>
+      <t>Population:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 일반 성인 </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>14</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Exposure/Condition:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 자외선 차단제 사용 (Sunscreen use)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Comparator:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 차단제 미사용자 또는 낮은 빈도 사용</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Result:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 자외선 차단제 사용은 주름 형성을 약 50% 감소시키는 보호 효과를 보임 </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>15</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Stats:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> pOR=0.50, 95% CI [0.25, 0.98] </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>16</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Design:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 메타분석 (관찰 연구 기반) </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>17</t>
+    </r>
+  </si>
+  <si>
+    <t>p03</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">자외선 차단제를 꾸준히 바르는 것은 주름 예방에 큰 도움이 됩니다. 연구에 따르면 자외선 차단제 사용자는 미사용자에 비해 주름 발생 위험이 절반 수준으로 낮아지는 보호 효과가 나타났습니다. </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>18</t>
+    </r>
+  </si>
+  <si>
+    <t>Topiwala_2022</t>
+  </si>
+  <si>
+    <t>Alcohol consumption and telomere length</t>
+  </si>
+  <si>
+    <t>RESULTS</t>
+  </si>
+  <si>
+    <t>Observational analysis</t>
+  </si>
+  <si>
+    <t>Compared to lowest quintile drinkers (&lt;6 units (48 g) weekly), highest quartile drinkers (&gt;29 units weekly (232 g)) had significantly shorter telomeres ($\beta$ -0.05, 95% CI: -0.06 to -0.03, $p=2.36\times10^{-11}$)... equivalent to 1–2 years of age-related change on telomere length.</t>
+  </si>
+  <si>
+    <t>alcohol_consumption</t>
+  </si>
+  <si>
+    <t>telomere_length</t>
+  </si>
+  <si>
+    <t>텔로미어 길이</t>
+  </si>
+  <si>
+    <t>adult, european_ancestry</t>
+  </si>
+  <si>
+    <t>유럽계 성인</t>
+  </si>
+  <si>
+    <t>observational_cohort_study</t>
+  </si>
+  <si>
+    <t>beta_coefficient</t>
+  </si>
+  <si>
+    <t>years_aging</t>
+  </si>
+  <si>
+    <r>
+      <t>Population:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 유럽계 성인 (n=245,354)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Exposure/Condition:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 고위험 음주 (주당 29단위 초과, 약 232g 이상)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Comparator:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 저위험 음주 (주당 6단위 미만)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Outcome:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> telomere_length (텔로미어 길이)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Result:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 과도한 음주는 텔로미어 길이를 유의미하게 단축시키며, 이는 약 1~2년의 추가적인 노화 가속화와 동일한 수준임 </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>111</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Stats:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> $\beta$=-0.05, 95% CI [-0.06, -0.03], p&lt;0.001</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Design:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 대규모 관찰 코호트 연구</t>
+    </r>
+  </si>
+  <si>
+    <t>&lt;0.001</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">일주일에 와인 10잔 이상의 술을 마시는 사람은 적게 마시는 사람보다 텔로미어 길이가 짧아지며, 이는 실제 나이보다 몸이 1~2년 더 늙은 것과 같은 상태임을 의미합니다. </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <t>Genetic analysis (MR)</t>
+  </si>
+  <si>
+    <t>In the AUD MR... there was a significant association with telomere length (IVW $\beta$ -0.07, 95% CI: -0.11 to -0.03, p=0.001)... 1 SD higher genetically-predicted log-transformed alcoholic drinks weekly was equivalent to 3 years of aging.</t>
+  </si>
+  <si>
+    <t>alcohol_use_disorder</t>
+  </si>
+  <si>
+    <t>mendelian_randomization</t>
+  </si>
+  <si>
+    <r>
+      <t>Population:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 유럽계 성인 (n=472,174 GWAS 데이터)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Exposure/Condition:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 유전적으로 예측된 음주량 증가 (1 SD 상승)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Comparator:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 유전적 음주 성향이 낮은 집단</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Result:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 유전적으로 예측된 음주량이 1 표준편차 증가할 때마다 텔로미어 길이가 짧아져 약 3년의 노화 가속화가 발생하는 인과관계가 확인됨 </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Stats:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> IVW $\beta$=-0.07, p=0.001</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Design:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 멘델 무작위 분석 (인과성 증명)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">유전적 분석 결과, 술을 더 많이 마시는 체질을 가진 사람들은 텔로미어 길이가 더 짧았으며, 이는 음주가 단순히 노화와 상관있는 것이 아니라 직접적으로 노화를 3년 정도 앞당기는 원인이 됨을 보여줍니다. </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <t>Non-linear MR (Threshold)</t>
+  </si>
+  <si>
+    <t>Non-linear MR analyses... associations were only significant in the highest two quintiles of alcohol consumption, equating to &gt;17 units weekly... In participants drinking smaller amounts, there was no association.</t>
+  </si>
+  <si>
+    <t>alcohol_threshold</t>
+  </si>
+  <si>
+    <t>SD_change</t>
+  </si>
+  <si>
+    <r>
+      <t>Population:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 유럽계 성인 음주자</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Exposure/Condition:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 주당 17단위 이상의 음주</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Comparator:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 주당 17단위 미만 음주자</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Result:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 음주량이 주당 17단위(에탄올 약 136g)를 넘어서는 시점부터 텔로미어가 급격히 짧아지는 '임계치 효과'가 나타남 </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>555</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Stats:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 17-28단위 구간 $\beta$=-0.17, p=0.013</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Design:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 비선형 멘델 무작위 분석</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">술이 노화에 미치는 영향에는 '문턱'이 있습니다. 일주일에 17단위(와인 약 6~7잔) 미만으로 마실 때는 노화 가속화가 뚜렷하지 않았으나, 이 수치를 넘기면 텔로미어 길이가 유의미하게 짧아지기 시작합니다. </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="6"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>6666</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2950,6 +3917,46 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="6"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="6"/>
+      <color rgb="FF444746"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2972,8 +3979,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3276,7 +4310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z138"/>
+  <dimension ref="A1:Z241"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -11345,7 +12379,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="129" spans="1:26" x14ac:dyDescent="0.6">
       <c r="A129" t="s">
         <v>742</v>
       </c>
@@ -11410,7 +12444,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="130" spans="1:26" x14ac:dyDescent="0.6">
       <c r="A130" t="s">
         <v>742</v>
       </c>
@@ -11475,7 +12509,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="131" spans="1:26" x14ac:dyDescent="0.6">
       <c r="A131" t="s">
         <v>742</v>
       </c>
@@ -11537,7 +12571,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="132" spans="1:26" x14ac:dyDescent="0.6">
       <c r="A132" t="s">
         <v>782</v>
       </c>
@@ -11596,7 +12630,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="133" spans="1:26" x14ac:dyDescent="0.6">
       <c r="A133" t="s">
         <v>782</v>
       </c>
@@ -11655,7 +12689,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="134" spans="1:26" x14ac:dyDescent="0.6">
       <c r="A134" t="s">
         <v>782</v>
       </c>
@@ -11714,7 +12748,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="135" spans="1:26" x14ac:dyDescent="0.6">
       <c r="A135" t="s">
         <v>782</v>
       </c>
@@ -11779,7 +12813,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="136" spans="1:26" x14ac:dyDescent="0.6">
       <c r="A136" t="s">
         <v>782</v>
       </c>
@@ -11844,7 +12878,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="137" spans="1:26" x14ac:dyDescent="0.6">
       <c r="A137" t="s">
         <v>782</v>
       </c>
@@ -11909,7 +12943,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.6">
+    <row r="138" spans="1:26" x14ac:dyDescent="0.6">
       <c r="A138" t="s">
         <v>782</v>
       </c>
@@ -11971,7 +13005,4011 @@
         <v>408</v>
       </c>
     </row>
+    <row r="139" spans="1:26" ht="40.5" x14ac:dyDescent="0.6">
+      <c r="A139" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="C139" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="I139" s="2">
+        <v>4</v>
+      </c>
+      <c r="J139" s="2">
+        <v>5</v>
+      </c>
+      <c r="K139" s="2"/>
+      <c r="L139" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="M139" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="N139" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="O139" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="P139" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="Q139" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="R139" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="S139" s="2">
+        <v>1</v>
+      </c>
+      <c r="T139" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="U139" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="V139" s="2">
+        <v>3.96</v>
+      </c>
+      <c r="W139" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="X139" s="2">
+        <v>1.75</v>
+      </c>
+      <c r="Y139" s="2">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="Z139" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A140" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="C140" s="4">
+        <v>2021</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="H140" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="I140" s="4">
+        <v>4</v>
+      </c>
+      <c r="J140" s="4">
+        <v>5</v>
+      </c>
+      <c r="K140" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="L140" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="M140" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="N140" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="O140" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="P140" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="Q140" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="R140" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="S140" s="4">
+        <v>1</v>
+      </c>
+      <c r="T140" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="U140" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="V140" s="4">
+        <v>3.96</v>
+      </c>
+      <c r="W140" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="X140" s="4">
+        <v>1.75</v>
+      </c>
+      <c r="Y140" s="4">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="Z140" s="4" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="141" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A141" s="4"/>
+      <c r="B141" s="4"/>
+      <c r="C141" s="4"/>
+      <c r="D141" s="4"/>
+      <c r="E141" s="4"/>
+      <c r="F141" s="4"/>
+      <c r="G141" s="4"/>
+      <c r="H141" s="4"/>
+      <c r="I141" s="4"/>
+      <c r="J141" s="4"/>
+      <c r="K141" s="4"/>
+      <c r="L141" s="1"/>
+      <c r="M141" s="4"/>
+      <c r="N141" s="4"/>
+      <c r="O141" s="4"/>
+      <c r="P141" s="4"/>
+      <c r="Q141" s="4"/>
+      <c r="R141" s="4"/>
+      <c r="S141" s="4"/>
+      <c r="T141" s="4"/>
+      <c r="U141" s="4"/>
+      <c r="V141" s="4"/>
+      <c r="W141" s="4"/>
+      <c r="X141" s="4"/>
+      <c r="Y141" s="4"/>
+      <c r="Z141" s="4"/>
+    </row>
+    <row r="142" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A142" s="4"/>
+      <c r="B142" s="4"/>
+      <c r="C142" s="4"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="4"/>
+      <c r="F142" s="4"/>
+      <c r="G142" s="4"/>
+      <c r="H142" s="4"/>
+      <c r="I142" s="4"/>
+      <c r="J142" s="4"/>
+      <c r="K142" s="4"/>
+      <c r="L142" s="1"/>
+      <c r="M142" s="4"/>
+      <c r="N142" s="4"/>
+      <c r="O142" s="4"/>
+      <c r="P142" s="4"/>
+      <c r="Q142" s="4"/>
+      <c r="R142" s="4"/>
+      <c r="S142" s="4"/>
+      <c r="T142" s="4"/>
+      <c r="U142" s="4"/>
+      <c r="V142" s="4"/>
+      <c r="W142" s="4"/>
+      <c r="X142" s="4"/>
+      <c r="Y142" s="4"/>
+      <c r="Z142" s="4"/>
+    </row>
+    <row r="143" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A143" s="4"/>
+      <c r="B143" s="4"/>
+      <c r="C143" s="4"/>
+      <c r="D143" s="4"/>
+      <c r="E143" s="4"/>
+      <c r="F143" s="4"/>
+      <c r="G143" s="4"/>
+      <c r="H143" s="4"/>
+      <c r="I143" s="4"/>
+      <c r="J143" s="4"/>
+      <c r="K143" s="4"/>
+      <c r="L143" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="M143" s="4"/>
+      <c r="N143" s="4"/>
+      <c r="O143" s="4"/>
+      <c r="P143" s="4"/>
+      <c r="Q143" s="4"/>
+      <c r="R143" s="4"/>
+      <c r="S143" s="4"/>
+      <c r="T143" s="4"/>
+      <c r="U143" s="4"/>
+      <c r="V143" s="4"/>
+      <c r="W143" s="4"/>
+      <c r="X143" s="4"/>
+      <c r="Y143" s="4"/>
+      <c r="Z143" s="4"/>
+    </row>
+    <row r="144" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A144" s="4"/>
+      <c r="B144" s="4"/>
+      <c r="C144" s="4"/>
+      <c r="D144" s="4"/>
+      <c r="E144" s="4"/>
+      <c r="F144" s="4"/>
+      <c r="G144" s="4"/>
+      <c r="H144" s="4"/>
+      <c r="I144" s="4"/>
+      <c r="J144" s="4"/>
+      <c r="K144" s="4"/>
+      <c r="L144" s="1"/>
+      <c r="M144" s="4"/>
+      <c r="N144" s="4"/>
+      <c r="O144" s="4"/>
+      <c r="P144" s="4"/>
+      <c r="Q144" s="4"/>
+      <c r="R144" s="4"/>
+      <c r="S144" s="4"/>
+      <c r="T144" s="4"/>
+      <c r="U144" s="4"/>
+      <c r="V144" s="4"/>
+      <c r="W144" s="4"/>
+      <c r="X144" s="4"/>
+      <c r="Y144" s="4"/>
+      <c r="Z144" s="4"/>
+    </row>
+    <row r="145" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A145" s="4"/>
+      <c r="B145" s="4"/>
+      <c r="C145" s="4"/>
+      <c r="D145" s="4"/>
+      <c r="E145" s="4"/>
+      <c r="F145" s="4"/>
+      <c r="G145" s="4"/>
+      <c r="H145" s="4"/>
+      <c r="I145" s="4"/>
+      <c r="J145" s="4"/>
+      <c r="K145" s="4"/>
+      <c r="L145" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="M145" s="4"/>
+      <c r="N145" s="4"/>
+      <c r="O145" s="4"/>
+      <c r="P145" s="4"/>
+      <c r="Q145" s="4"/>
+      <c r="R145" s="4"/>
+      <c r="S145" s="4"/>
+      <c r="T145" s="4"/>
+      <c r="U145" s="4"/>
+      <c r="V145" s="4"/>
+      <c r="W145" s="4"/>
+      <c r="X145" s="4"/>
+      <c r="Y145" s="4"/>
+      <c r="Z145" s="4"/>
+    </row>
+    <row r="146" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A146" s="4"/>
+      <c r="B146" s="4"/>
+      <c r="C146" s="4"/>
+      <c r="D146" s="4"/>
+      <c r="E146" s="4"/>
+      <c r="F146" s="4"/>
+      <c r="G146" s="4"/>
+      <c r="H146" s="4"/>
+      <c r="I146" s="4"/>
+      <c r="J146" s="4"/>
+      <c r="K146" s="4"/>
+      <c r="L146" s="1"/>
+      <c r="M146" s="4"/>
+      <c r="N146" s="4"/>
+      <c r="O146" s="4"/>
+      <c r="P146" s="4"/>
+      <c r="Q146" s="4"/>
+      <c r="R146" s="4"/>
+      <c r="S146" s="4"/>
+      <c r="T146" s="4"/>
+      <c r="U146" s="4"/>
+      <c r="V146" s="4"/>
+      <c r="W146" s="4"/>
+      <c r="X146" s="4"/>
+      <c r="Y146" s="4"/>
+      <c r="Z146" s="4"/>
+    </row>
+    <row r="147" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A147" s="4"/>
+      <c r="B147" s="4"/>
+      <c r="C147" s="4"/>
+      <c r="D147" s="4"/>
+      <c r="E147" s="4"/>
+      <c r="F147" s="4"/>
+      <c r="G147" s="4"/>
+      <c r="H147" s="4"/>
+      <c r="I147" s="4"/>
+      <c r="J147" s="4"/>
+      <c r="K147" s="4"/>
+      <c r="L147" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="M147" s="4"/>
+      <c r="N147" s="4"/>
+      <c r="O147" s="4"/>
+      <c r="P147" s="4"/>
+      <c r="Q147" s="4"/>
+      <c r="R147" s="4"/>
+      <c r="S147" s="4"/>
+      <c r="T147" s="4"/>
+      <c r="U147" s="4"/>
+      <c r="V147" s="4"/>
+      <c r="W147" s="4"/>
+      <c r="X147" s="4"/>
+      <c r="Y147" s="4"/>
+      <c r="Z147" s="4"/>
+    </row>
+    <row r="148" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A148" s="4"/>
+      <c r="B148" s="4"/>
+      <c r="C148" s="4"/>
+      <c r="D148" s="4"/>
+      <c r="E148" s="4"/>
+      <c r="F148" s="4"/>
+      <c r="G148" s="4"/>
+      <c r="H148" s="4"/>
+      <c r="I148" s="4"/>
+      <c r="J148" s="4"/>
+      <c r="K148" s="4"/>
+      <c r="L148" s="1"/>
+      <c r="M148" s="4"/>
+      <c r="N148" s="4"/>
+      <c r="O148" s="4"/>
+      <c r="P148" s="4"/>
+      <c r="Q148" s="4"/>
+      <c r="R148" s="4"/>
+      <c r="S148" s="4"/>
+      <c r="T148" s="4"/>
+      <c r="U148" s="4"/>
+      <c r="V148" s="4"/>
+      <c r="W148" s="4"/>
+      <c r="X148" s="4"/>
+      <c r="Y148" s="4"/>
+      <c r="Z148" s="4"/>
+    </row>
+    <row r="149" spans="1:26" ht="27.4" x14ac:dyDescent="0.6">
+      <c r="A149" s="4"/>
+      <c r="B149" s="4"/>
+      <c r="C149" s="4"/>
+      <c r="D149" s="4"/>
+      <c r="E149" s="4"/>
+      <c r="F149" s="4"/>
+      <c r="G149" s="4"/>
+      <c r="H149" s="4"/>
+      <c r="I149" s="4"/>
+      <c r="J149" s="4"/>
+      <c r="K149" s="4"/>
+      <c r="L149" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="M149" s="4"/>
+      <c r="N149" s="4"/>
+      <c r="O149" s="4"/>
+      <c r="P149" s="4"/>
+      <c r="Q149" s="4"/>
+      <c r="R149" s="4"/>
+      <c r="S149" s="4"/>
+      <c r="T149" s="4"/>
+      <c r="U149" s="4"/>
+      <c r="V149" s="4"/>
+      <c r="W149" s="4"/>
+      <c r="X149" s="4"/>
+      <c r="Y149" s="4"/>
+      <c r="Z149" s="4"/>
+    </row>
+    <row r="150" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A150" s="4"/>
+      <c r="B150" s="4"/>
+      <c r="C150" s="4"/>
+      <c r="D150" s="4"/>
+      <c r="E150" s="4"/>
+      <c r="F150" s="4"/>
+      <c r="G150" s="4"/>
+      <c r="H150" s="4"/>
+      <c r="I150" s="4"/>
+      <c r="J150" s="4"/>
+      <c r="K150" s="4"/>
+      <c r="L150" s="1"/>
+      <c r="M150" s="4"/>
+      <c r="N150" s="4"/>
+      <c r="O150" s="4"/>
+      <c r="P150" s="4"/>
+      <c r="Q150" s="4"/>
+      <c r="R150" s="4"/>
+      <c r="S150" s="4"/>
+      <c r="T150" s="4"/>
+      <c r="U150" s="4"/>
+      <c r="V150" s="4"/>
+      <c r="W150" s="4"/>
+      <c r="X150" s="4"/>
+      <c r="Y150" s="4"/>
+      <c r="Z150" s="4"/>
+    </row>
+    <row r="151" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A151" s="4"/>
+      <c r="B151" s="4"/>
+      <c r="C151" s="4"/>
+      <c r="D151" s="4"/>
+      <c r="E151" s="4"/>
+      <c r="F151" s="4"/>
+      <c r="G151" s="4"/>
+      <c r="H151" s="4"/>
+      <c r="I151" s="4"/>
+      <c r="J151" s="4"/>
+      <c r="K151" s="4"/>
+      <c r="L151" s="1"/>
+      <c r="M151" s="4"/>
+      <c r="N151" s="4"/>
+      <c r="O151" s="4"/>
+      <c r="P151" s="4"/>
+      <c r="Q151" s="4"/>
+      <c r="R151" s="4"/>
+      <c r="S151" s="4"/>
+      <c r="T151" s="4"/>
+      <c r="U151" s="4"/>
+      <c r="V151" s="4"/>
+      <c r="W151" s="4"/>
+      <c r="X151" s="4"/>
+      <c r="Y151" s="4"/>
+      <c r="Z151" s="4"/>
+    </row>
+    <row r="152" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A152" s="4"/>
+      <c r="B152" s="4"/>
+      <c r="C152" s="4"/>
+      <c r="D152" s="4"/>
+      <c r="E152" s="4"/>
+      <c r="F152" s="4"/>
+      <c r="G152" s="4"/>
+      <c r="H152" s="4"/>
+      <c r="I152" s="4"/>
+      <c r="J152" s="4"/>
+      <c r="K152" s="4"/>
+      <c r="L152" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="M152" s="4"/>
+      <c r="N152" s="4"/>
+      <c r="O152" s="4"/>
+      <c r="P152" s="4"/>
+      <c r="Q152" s="4"/>
+      <c r="R152" s="4"/>
+      <c r="S152" s="4"/>
+      <c r="T152" s="4"/>
+      <c r="U152" s="4"/>
+      <c r="V152" s="4"/>
+      <c r="W152" s="4"/>
+      <c r="X152" s="4"/>
+      <c r="Y152" s="4"/>
+      <c r="Z152" s="4"/>
+    </row>
+    <row r="153" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A153" s="4"/>
+      <c r="B153" s="4"/>
+      <c r="C153" s="4"/>
+      <c r="D153" s="4"/>
+      <c r="E153" s="4"/>
+      <c r="F153" s="4"/>
+      <c r="G153" s="4"/>
+      <c r="H153" s="4"/>
+      <c r="I153" s="4"/>
+      <c r="J153" s="4"/>
+      <c r="K153" s="4"/>
+      <c r="L153" s="1"/>
+      <c r="M153" s="4"/>
+      <c r="N153" s="4"/>
+      <c r="O153" s="4"/>
+      <c r="P153" s="4"/>
+      <c r="Q153" s="4"/>
+      <c r="R153" s="4"/>
+      <c r="S153" s="4"/>
+      <c r="T153" s="4"/>
+      <c r="U153" s="4"/>
+      <c r="V153" s="4"/>
+      <c r="W153" s="4"/>
+      <c r="X153" s="4"/>
+      <c r="Y153" s="4"/>
+      <c r="Z153" s="4"/>
+    </row>
+    <row r="154" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A154" s="4"/>
+      <c r="B154" s="4"/>
+      <c r="C154" s="4"/>
+      <c r="D154" s="4"/>
+      <c r="E154" s="4"/>
+      <c r="F154" s="4"/>
+      <c r="G154" s="4"/>
+      <c r="H154" s="4"/>
+      <c r="I154" s="4"/>
+      <c r="J154" s="4"/>
+      <c r="K154" s="4"/>
+      <c r="L154" s="1"/>
+      <c r="M154" s="4"/>
+      <c r="N154" s="4"/>
+      <c r="O154" s="4"/>
+      <c r="P154" s="4"/>
+      <c r="Q154" s="4"/>
+      <c r="R154" s="4"/>
+      <c r="S154" s="4"/>
+      <c r="T154" s="4"/>
+      <c r="U154" s="4"/>
+      <c r="V154" s="4"/>
+      <c r="W154" s="4"/>
+      <c r="X154" s="4"/>
+      <c r="Y154" s="4"/>
+      <c r="Z154" s="4"/>
+    </row>
+    <row r="155" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A155" s="4"/>
+      <c r="B155" s="4"/>
+      <c r="C155" s="4"/>
+      <c r="D155" s="4"/>
+      <c r="E155" s="4"/>
+      <c r="F155" s="4"/>
+      <c r="G155" s="4"/>
+      <c r="H155" s="4"/>
+      <c r="I155" s="4"/>
+      <c r="J155" s="4"/>
+      <c r="K155" s="4"/>
+      <c r="L155" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="M155" s="4"/>
+      <c r="N155" s="4"/>
+      <c r="O155" s="4"/>
+      <c r="P155" s="4"/>
+      <c r="Q155" s="4"/>
+      <c r="R155" s="4"/>
+      <c r="S155" s="4"/>
+      <c r="T155" s="4"/>
+      <c r="U155" s="4"/>
+      <c r="V155" s="4"/>
+      <c r="W155" s="4"/>
+      <c r="X155" s="4"/>
+      <c r="Y155" s="4"/>
+      <c r="Z155" s="4"/>
+    </row>
+    <row r="156" spans="1:26" ht="40.5" x14ac:dyDescent="0.6">
+      <c r="A156" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="C156" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="I156" s="2">
+        <v>4</v>
+      </c>
+      <c r="J156" s="2">
+        <v>5</v>
+      </c>
+      <c r="K156" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="L156" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="M156" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="N156" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="O156" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="P156" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="Q156" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="R156" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="S156" s="2">
+        <v>1</v>
+      </c>
+      <c r="T156" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="U156" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="V156" s="2">
+        <v>3.96</v>
+      </c>
+      <c r="W156" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="X156" s="2"/>
+      <c r="Y156" s="2"/>
+      <c r="Z156" s="2" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="157" spans="1:26" ht="40.5" x14ac:dyDescent="0.6">
+      <c r="A157" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="C157" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="I157" s="2">
+        <v>8</v>
+      </c>
+      <c r="J157" s="2">
+        <v>8</v>
+      </c>
+      <c r="K157" s="2"/>
+      <c r="L157" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="M157" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="N157" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="O157" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="P157" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="Q157" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="R157" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="S157" s="2">
+        <v>1</v>
+      </c>
+      <c r="T157" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="U157" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="V157" s="2">
+        <v>3.21</v>
+      </c>
+      <c r="W157" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="X157" s="2">
+        <v>1.56</v>
+      </c>
+      <c r="Y157" s="2">
+        <v>6.58</v>
+      </c>
+      <c r="Z157" s="2">
+        <v>0.14099999999999999</v>
+      </c>
+    </row>
+    <row r="158" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A158" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="C158" s="4">
+        <v>2021</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E158" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="G158" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="H158" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="I158" s="4">
+        <v>8</v>
+      </c>
+      <c r="J158" s="4">
+        <v>8</v>
+      </c>
+      <c r="K158" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="L158" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="M158" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="N158" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="O158" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="P158" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="Q158" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="R158" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="S158" s="4">
+        <v>1</v>
+      </c>
+      <c r="T158" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="U158" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="V158" s="4">
+        <v>3.21</v>
+      </c>
+      <c r="W158" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="X158" s="4">
+        <v>1.56</v>
+      </c>
+      <c r="Y158" s="4">
+        <v>6.58</v>
+      </c>
+      <c r="Z158" s="4">
+        <v>0.14099999999999999</v>
+      </c>
+    </row>
+    <row r="159" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A159" s="4"/>
+      <c r="B159" s="4"/>
+      <c r="C159" s="4"/>
+      <c r="D159" s="4"/>
+      <c r="E159" s="4"/>
+      <c r="F159" s="4"/>
+      <c r="G159" s="4"/>
+      <c r="H159" s="4"/>
+      <c r="I159" s="4"/>
+      <c r="J159" s="4"/>
+      <c r="K159" s="4"/>
+      <c r="L159" s="1"/>
+      <c r="M159" s="4"/>
+      <c r="N159" s="4"/>
+      <c r="O159" s="4"/>
+      <c r="P159" s="4"/>
+      <c r="Q159" s="4"/>
+      <c r="R159" s="4"/>
+      <c r="S159" s="4"/>
+      <c r="T159" s="4"/>
+      <c r="U159" s="4"/>
+      <c r="V159" s="4"/>
+      <c r="W159" s="4"/>
+      <c r="X159" s="4"/>
+      <c r="Y159" s="4"/>
+      <c r="Z159" s="4"/>
+    </row>
+    <row r="160" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A160" s="4"/>
+      <c r="B160" s="4"/>
+      <c r="C160" s="4"/>
+      <c r="D160" s="4"/>
+      <c r="E160" s="4"/>
+      <c r="F160" s="4"/>
+      <c r="G160" s="4"/>
+      <c r="H160" s="4"/>
+      <c r="I160" s="4"/>
+      <c r="J160" s="4"/>
+      <c r="K160" s="4"/>
+      <c r="L160" s="1"/>
+      <c r="M160" s="4"/>
+      <c r="N160" s="4"/>
+      <c r="O160" s="4"/>
+      <c r="P160" s="4"/>
+      <c r="Q160" s="4"/>
+      <c r="R160" s="4"/>
+      <c r="S160" s="4"/>
+      <c r="T160" s="4"/>
+      <c r="U160" s="4"/>
+      <c r="V160" s="4"/>
+      <c r="W160" s="4"/>
+      <c r="X160" s="4"/>
+      <c r="Y160" s="4"/>
+      <c r="Z160" s="4"/>
+    </row>
+    <row r="161" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A161" s="4"/>
+      <c r="B161" s="4"/>
+      <c r="C161" s="4"/>
+      <c r="D161" s="4"/>
+      <c r="E161" s="4"/>
+      <c r="F161" s="4"/>
+      <c r="G161" s="4"/>
+      <c r="H161" s="4"/>
+      <c r="I161" s="4"/>
+      <c r="J161" s="4"/>
+      <c r="K161" s="4"/>
+      <c r="L161" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="M161" s="4"/>
+      <c r="N161" s="4"/>
+      <c r="O161" s="4"/>
+      <c r="P161" s="4"/>
+      <c r="Q161" s="4"/>
+      <c r="R161" s="4"/>
+      <c r="S161" s="4"/>
+      <c r="T161" s="4"/>
+      <c r="U161" s="4"/>
+      <c r="V161" s="4"/>
+      <c r="W161" s="4"/>
+      <c r="X161" s="4"/>
+      <c r="Y161" s="4"/>
+      <c r="Z161" s="4"/>
+    </row>
+    <row r="162" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A162" s="4"/>
+      <c r="B162" s="4"/>
+      <c r="C162" s="4"/>
+      <c r="D162" s="4"/>
+      <c r="E162" s="4"/>
+      <c r="F162" s="4"/>
+      <c r="G162" s="4"/>
+      <c r="H162" s="4"/>
+      <c r="I162" s="4"/>
+      <c r="J162" s="4"/>
+      <c r="K162" s="4"/>
+      <c r="L162" s="1"/>
+      <c r="M162" s="4"/>
+      <c r="N162" s="4"/>
+      <c r="O162" s="4"/>
+      <c r="P162" s="4"/>
+      <c r="Q162" s="4"/>
+      <c r="R162" s="4"/>
+      <c r="S162" s="4"/>
+      <c r="T162" s="4"/>
+      <c r="U162" s="4"/>
+      <c r="V162" s="4"/>
+      <c r="W162" s="4"/>
+      <c r="X162" s="4"/>
+      <c r="Y162" s="4"/>
+      <c r="Z162" s="4"/>
+    </row>
+    <row r="163" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A163" s="4"/>
+      <c r="B163" s="4"/>
+      <c r="C163" s="4"/>
+      <c r="D163" s="4"/>
+      <c r="E163" s="4"/>
+      <c r="F163" s="4"/>
+      <c r="G163" s="4"/>
+      <c r="H163" s="4"/>
+      <c r="I163" s="4"/>
+      <c r="J163" s="4"/>
+      <c r="K163" s="4"/>
+      <c r="L163" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="M163" s="4"/>
+      <c r="N163" s="4"/>
+      <c r="O163" s="4"/>
+      <c r="P163" s="4"/>
+      <c r="Q163" s="4"/>
+      <c r="R163" s="4"/>
+      <c r="S163" s="4"/>
+      <c r="T163" s="4"/>
+      <c r="U163" s="4"/>
+      <c r="V163" s="4"/>
+      <c r="W163" s="4"/>
+      <c r="X163" s="4"/>
+      <c r="Y163" s="4"/>
+      <c r="Z163" s="4"/>
+    </row>
+    <row r="164" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A164" s="4"/>
+      <c r="B164" s="4"/>
+      <c r="C164" s="4"/>
+      <c r="D164" s="4"/>
+      <c r="E164" s="4"/>
+      <c r="F164" s="4"/>
+      <c r="G164" s="4"/>
+      <c r="H164" s="4"/>
+      <c r="I164" s="4"/>
+      <c r="J164" s="4"/>
+      <c r="K164" s="4"/>
+      <c r="L164" s="1"/>
+      <c r="M164" s="4"/>
+      <c r="N164" s="4"/>
+      <c r="O164" s="4"/>
+      <c r="P164" s="4"/>
+      <c r="Q164" s="4"/>
+      <c r="R164" s="4"/>
+      <c r="S164" s="4"/>
+      <c r="T164" s="4"/>
+      <c r="U164" s="4"/>
+      <c r="V164" s="4"/>
+      <c r="W164" s="4"/>
+      <c r="X164" s="4"/>
+      <c r="Y164" s="4"/>
+      <c r="Z164" s="4"/>
+    </row>
+    <row r="165" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A165" s="4"/>
+      <c r="B165" s="4"/>
+      <c r="C165" s="4"/>
+      <c r="D165" s="4"/>
+      <c r="E165" s="4"/>
+      <c r="F165" s="4"/>
+      <c r="G165" s="4"/>
+      <c r="H165" s="4"/>
+      <c r="I165" s="4"/>
+      <c r="J165" s="4"/>
+      <c r="K165" s="4"/>
+      <c r="L165" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="M165" s="4"/>
+      <c r="N165" s="4"/>
+      <c r="O165" s="4"/>
+      <c r="P165" s="4"/>
+      <c r="Q165" s="4"/>
+      <c r="R165" s="4"/>
+      <c r="S165" s="4"/>
+      <c r="T165" s="4"/>
+      <c r="U165" s="4"/>
+      <c r="V165" s="4"/>
+      <c r="W165" s="4"/>
+      <c r="X165" s="4"/>
+      <c r="Y165" s="4"/>
+      <c r="Z165" s="4"/>
+    </row>
+    <row r="166" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A166" s="4"/>
+      <c r="B166" s="4"/>
+      <c r="C166" s="4"/>
+      <c r="D166" s="4"/>
+      <c r="E166" s="4"/>
+      <c r="F166" s="4"/>
+      <c r="G166" s="4"/>
+      <c r="H166" s="4"/>
+      <c r="I166" s="4"/>
+      <c r="J166" s="4"/>
+      <c r="K166" s="4"/>
+      <c r="L166" s="1"/>
+      <c r="M166" s="4"/>
+      <c r="N166" s="4"/>
+      <c r="O166" s="4"/>
+      <c r="P166" s="4"/>
+      <c r="Q166" s="4"/>
+      <c r="R166" s="4"/>
+      <c r="S166" s="4"/>
+      <c r="T166" s="4"/>
+      <c r="U166" s="4"/>
+      <c r="V166" s="4"/>
+      <c r="W166" s="4"/>
+      <c r="X166" s="4"/>
+      <c r="Y166" s="4"/>
+      <c r="Z166" s="4"/>
+    </row>
+    <row r="167" spans="1:26" ht="27.4" x14ac:dyDescent="0.6">
+      <c r="A167" s="4"/>
+      <c r="B167" s="4"/>
+      <c r="C167" s="4"/>
+      <c r="D167" s="4"/>
+      <c r="E167" s="4"/>
+      <c r="F167" s="4"/>
+      <c r="G167" s="4"/>
+      <c r="H167" s="4"/>
+      <c r="I167" s="4"/>
+      <c r="J167" s="4"/>
+      <c r="K167" s="4"/>
+      <c r="L167" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="M167" s="4"/>
+      <c r="N167" s="4"/>
+      <c r="O167" s="4"/>
+      <c r="P167" s="4"/>
+      <c r="Q167" s="4"/>
+      <c r="R167" s="4"/>
+      <c r="S167" s="4"/>
+      <c r="T167" s="4"/>
+      <c r="U167" s="4"/>
+      <c r="V167" s="4"/>
+      <c r="W167" s="4"/>
+      <c r="X167" s="4"/>
+      <c r="Y167" s="4"/>
+      <c r="Z167" s="4"/>
+    </row>
+    <row r="168" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A168" s="4"/>
+      <c r="B168" s="4"/>
+      <c r="C168" s="4"/>
+      <c r="D168" s="4"/>
+      <c r="E168" s="4"/>
+      <c r="F168" s="4"/>
+      <c r="G168" s="4"/>
+      <c r="H168" s="4"/>
+      <c r="I168" s="4"/>
+      <c r="J168" s="4"/>
+      <c r="K168" s="4"/>
+      <c r="L168" s="1"/>
+      <c r="M168" s="4"/>
+      <c r="N168" s="4"/>
+      <c r="O168" s="4"/>
+      <c r="P168" s="4"/>
+      <c r="Q168" s="4"/>
+      <c r="R168" s="4"/>
+      <c r="S168" s="4"/>
+      <c r="T168" s="4"/>
+      <c r="U168" s="4"/>
+      <c r="V168" s="4"/>
+      <c r="W168" s="4"/>
+      <c r="X168" s="4"/>
+      <c r="Y168" s="4"/>
+      <c r="Z168" s="4"/>
+    </row>
+    <row r="169" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A169" s="4"/>
+      <c r="B169" s="4"/>
+      <c r="C169" s="4"/>
+      <c r="D169" s="4"/>
+      <c r="E169" s="4"/>
+      <c r="F169" s="4"/>
+      <c r="G169" s="4"/>
+      <c r="H169" s="4"/>
+      <c r="I169" s="4"/>
+      <c r="J169" s="4"/>
+      <c r="K169" s="4"/>
+      <c r="L169" s="1"/>
+      <c r="M169" s="4"/>
+      <c r="N169" s="4"/>
+      <c r="O169" s="4"/>
+      <c r="P169" s="4"/>
+      <c r="Q169" s="4"/>
+      <c r="R169" s="4"/>
+      <c r="S169" s="4"/>
+      <c r="T169" s="4"/>
+      <c r="U169" s="4"/>
+      <c r="V169" s="4"/>
+      <c r="W169" s="4"/>
+      <c r="X169" s="4"/>
+      <c r="Y169" s="4"/>
+      <c r="Z169" s="4"/>
+    </row>
+    <row r="170" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A170" s="4"/>
+      <c r="B170" s="4"/>
+      <c r="C170" s="4"/>
+      <c r="D170" s="4"/>
+      <c r="E170" s="4"/>
+      <c r="F170" s="4"/>
+      <c r="G170" s="4"/>
+      <c r="H170" s="4"/>
+      <c r="I170" s="4"/>
+      <c r="J170" s="4"/>
+      <c r="K170" s="4"/>
+      <c r="L170" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="M170" s="4"/>
+      <c r="N170" s="4"/>
+      <c r="O170" s="4"/>
+      <c r="P170" s="4"/>
+      <c r="Q170" s="4"/>
+      <c r="R170" s="4"/>
+      <c r="S170" s="4"/>
+      <c r="T170" s="4"/>
+      <c r="U170" s="4"/>
+      <c r="V170" s="4"/>
+      <c r="W170" s="4"/>
+      <c r="X170" s="4"/>
+      <c r="Y170" s="4"/>
+      <c r="Z170" s="4"/>
+    </row>
+    <row r="171" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A171" s="4"/>
+      <c r="B171" s="4"/>
+      <c r="C171" s="4"/>
+      <c r="D171" s="4"/>
+      <c r="E171" s="4"/>
+      <c r="F171" s="4"/>
+      <c r="G171" s="4"/>
+      <c r="H171" s="4"/>
+      <c r="I171" s="4"/>
+      <c r="J171" s="4"/>
+      <c r="K171" s="4"/>
+      <c r="L171" s="1"/>
+      <c r="M171" s="4"/>
+      <c r="N171" s="4"/>
+      <c r="O171" s="4"/>
+      <c r="P171" s="4"/>
+      <c r="Q171" s="4"/>
+      <c r="R171" s="4"/>
+      <c r="S171" s="4"/>
+      <c r="T171" s="4"/>
+      <c r="U171" s="4"/>
+      <c r="V171" s="4"/>
+      <c r="W171" s="4"/>
+      <c r="X171" s="4"/>
+      <c r="Y171" s="4"/>
+      <c r="Z171" s="4"/>
+    </row>
+    <row r="172" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A172" s="4"/>
+      <c r="B172" s="4"/>
+      <c r="C172" s="4"/>
+      <c r="D172" s="4"/>
+      <c r="E172" s="4"/>
+      <c r="F172" s="4"/>
+      <c r="G172" s="4"/>
+      <c r="H172" s="4"/>
+      <c r="I172" s="4"/>
+      <c r="J172" s="4"/>
+      <c r="K172" s="4"/>
+      <c r="L172" s="1"/>
+      <c r="M172" s="4"/>
+      <c r="N172" s="4"/>
+      <c r="O172" s="4"/>
+      <c r="P172" s="4"/>
+      <c r="Q172" s="4"/>
+      <c r="R172" s="4"/>
+      <c r="S172" s="4"/>
+      <c r="T172" s="4"/>
+      <c r="U172" s="4"/>
+      <c r="V172" s="4"/>
+      <c r="W172" s="4"/>
+      <c r="X172" s="4"/>
+      <c r="Y172" s="4"/>
+      <c r="Z172" s="4"/>
+    </row>
+    <row r="173" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A173" s="4"/>
+      <c r="B173" s="4"/>
+      <c r="C173" s="4"/>
+      <c r="D173" s="4"/>
+      <c r="E173" s="4"/>
+      <c r="F173" s="4"/>
+      <c r="G173" s="4"/>
+      <c r="H173" s="4"/>
+      <c r="I173" s="4"/>
+      <c r="J173" s="4"/>
+      <c r="K173" s="4"/>
+      <c r="L173" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="M173" s="4"/>
+      <c r="N173" s="4"/>
+      <c r="O173" s="4"/>
+      <c r="P173" s="4"/>
+      <c r="Q173" s="4"/>
+      <c r="R173" s="4"/>
+      <c r="S173" s="4"/>
+      <c r="T173" s="4"/>
+      <c r="U173" s="4"/>
+      <c r="V173" s="4"/>
+      <c r="W173" s="4"/>
+      <c r="X173" s="4"/>
+      <c r="Y173" s="4"/>
+      <c r="Z173" s="4"/>
+    </row>
+    <row r="174" spans="1:26" ht="40.5" x14ac:dyDescent="0.6">
+      <c r="A174" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="C174" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="I174" s="2">
+        <v>8</v>
+      </c>
+      <c r="J174" s="2">
+        <v>8</v>
+      </c>
+      <c r="K174" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="L174" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="M174" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="N174" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="O174" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="P174" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="Q174" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="R174" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="S174" s="2">
+        <v>1</v>
+      </c>
+      <c r="T174" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="U174" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="V174" s="2">
+        <v>3.21</v>
+      </c>
+      <c r="W174" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="X174" s="2"/>
+      <c r="Y174" s="2"/>
+      <c r="Z174" s="2"/>
+    </row>
+    <row r="175" spans="1:26" ht="40.5" x14ac:dyDescent="0.6">
+      <c r="A175" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="C175" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="I175" s="2">
+        <v>9</v>
+      </c>
+      <c r="J175" s="2">
+        <v>9</v>
+      </c>
+      <c r="K175" s="2"/>
+      <c r="L175" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="M175" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="N175" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="O175" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="P175" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="Q175" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="R175" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="S175" s="2">
+        <v>1</v>
+      </c>
+      <c r="T175" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="U175" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="V175" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="W175" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="X175" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="Y175" s="2">
+        <v>0.98</v>
+      </c>
+      <c r="Z175" s="2">
+        <v>0.38700000000000001</v>
+      </c>
+    </row>
+    <row r="176" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A176" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="C176" s="4">
+        <v>2021</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E176" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="G176" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="H176" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="I176" s="4">
+        <v>9</v>
+      </c>
+      <c r="J176" s="4">
+        <v>9</v>
+      </c>
+      <c r="K176" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="L176" s="3" t="s">
+        <v>876</v>
+      </c>
+      <c r="M176" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="N176" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="O176" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="P176" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="Q176" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="R176" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="S176" s="4">
+        <v>1</v>
+      </c>
+      <c r="T176" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="U176" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="V176" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="W176" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="X176" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="Y176" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="Z176" s="4">
+        <v>0.38700000000000001</v>
+      </c>
+    </row>
+    <row r="177" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A177" s="4"/>
+      <c r="B177" s="4"/>
+      <c r="C177" s="4"/>
+      <c r="D177" s="4"/>
+      <c r="E177" s="4"/>
+      <c r="F177" s="4"/>
+      <c r="G177" s="4"/>
+      <c r="H177" s="4"/>
+      <c r="I177" s="4"/>
+      <c r="J177" s="4"/>
+      <c r="K177" s="4"/>
+      <c r="L177" s="1"/>
+      <c r="M177" s="4"/>
+      <c r="N177" s="4"/>
+      <c r="O177" s="4"/>
+      <c r="P177" s="4"/>
+      <c r="Q177" s="4"/>
+      <c r="R177" s="4"/>
+      <c r="S177" s="4"/>
+      <c r="T177" s="4"/>
+      <c r="U177" s="4"/>
+      <c r="V177" s="4"/>
+      <c r="W177" s="4"/>
+      <c r="X177" s="4"/>
+      <c r="Y177" s="4"/>
+      <c r="Z177" s="4"/>
+    </row>
+    <row r="178" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A178" s="4"/>
+      <c r="B178" s="4"/>
+      <c r="C178" s="4"/>
+      <c r="D178" s="4"/>
+      <c r="E178" s="4"/>
+      <c r="F178" s="4"/>
+      <c r="G178" s="4"/>
+      <c r="H178" s="4"/>
+      <c r="I178" s="4"/>
+      <c r="J178" s="4"/>
+      <c r="K178" s="4"/>
+      <c r="L178" s="1"/>
+      <c r="M178" s="4"/>
+      <c r="N178" s="4"/>
+      <c r="O178" s="4"/>
+      <c r="P178" s="4"/>
+      <c r="Q178" s="4"/>
+      <c r="R178" s="4"/>
+      <c r="S178" s="4"/>
+      <c r="T178" s="4"/>
+      <c r="U178" s="4"/>
+      <c r="V178" s="4"/>
+      <c r="W178" s="4"/>
+      <c r="X178" s="4"/>
+      <c r="Y178" s="4"/>
+      <c r="Z178" s="4"/>
+    </row>
+    <row r="179" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A179" s="4"/>
+      <c r="B179" s="4"/>
+      <c r="C179" s="4"/>
+      <c r="D179" s="4"/>
+      <c r="E179" s="4"/>
+      <c r="F179" s="4"/>
+      <c r="G179" s="4"/>
+      <c r="H179" s="4"/>
+      <c r="I179" s="4"/>
+      <c r="J179" s="4"/>
+      <c r="K179" s="4"/>
+      <c r="L179" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="M179" s="4"/>
+      <c r="N179" s="4"/>
+      <c r="O179" s="4"/>
+      <c r="P179" s="4"/>
+      <c r="Q179" s="4"/>
+      <c r="R179" s="4"/>
+      <c r="S179" s="4"/>
+      <c r="T179" s="4"/>
+      <c r="U179" s="4"/>
+      <c r="V179" s="4"/>
+      <c r="W179" s="4"/>
+      <c r="X179" s="4"/>
+      <c r="Y179" s="4"/>
+      <c r="Z179" s="4"/>
+    </row>
+    <row r="180" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A180" s="4"/>
+      <c r="B180" s="4"/>
+      <c r="C180" s="4"/>
+      <c r="D180" s="4"/>
+      <c r="E180" s="4"/>
+      <c r="F180" s="4"/>
+      <c r="G180" s="4"/>
+      <c r="H180" s="4"/>
+      <c r="I180" s="4"/>
+      <c r="J180" s="4"/>
+      <c r="K180" s="4"/>
+      <c r="L180" s="1"/>
+      <c r="M180" s="4"/>
+      <c r="N180" s="4"/>
+      <c r="O180" s="4"/>
+      <c r="P180" s="4"/>
+      <c r="Q180" s="4"/>
+      <c r="R180" s="4"/>
+      <c r="S180" s="4"/>
+      <c r="T180" s="4"/>
+      <c r="U180" s="4"/>
+      <c r="V180" s="4"/>
+      <c r="W180" s="4"/>
+      <c r="X180" s="4"/>
+      <c r="Y180" s="4"/>
+      <c r="Z180" s="4"/>
+    </row>
+    <row r="181" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A181" s="4"/>
+      <c r="B181" s="4"/>
+      <c r="C181" s="4"/>
+      <c r="D181" s="4"/>
+      <c r="E181" s="4"/>
+      <c r="F181" s="4"/>
+      <c r="G181" s="4"/>
+      <c r="H181" s="4"/>
+      <c r="I181" s="4"/>
+      <c r="J181" s="4"/>
+      <c r="K181" s="4"/>
+      <c r="L181" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="M181" s="4"/>
+      <c r="N181" s="4"/>
+      <c r="O181" s="4"/>
+      <c r="P181" s="4"/>
+      <c r="Q181" s="4"/>
+      <c r="R181" s="4"/>
+      <c r="S181" s="4"/>
+      <c r="T181" s="4"/>
+      <c r="U181" s="4"/>
+      <c r="V181" s="4"/>
+      <c r="W181" s="4"/>
+      <c r="X181" s="4"/>
+      <c r="Y181" s="4"/>
+      <c r="Z181" s="4"/>
+    </row>
+    <row r="182" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A182" s="4"/>
+      <c r="B182" s="4"/>
+      <c r="C182" s="4"/>
+      <c r="D182" s="4"/>
+      <c r="E182" s="4"/>
+      <c r="F182" s="4"/>
+      <c r="G182" s="4"/>
+      <c r="H182" s="4"/>
+      <c r="I182" s="4"/>
+      <c r="J182" s="4"/>
+      <c r="K182" s="4"/>
+      <c r="L182" s="1"/>
+      <c r="M182" s="4"/>
+      <c r="N182" s="4"/>
+      <c r="O182" s="4"/>
+      <c r="P182" s="4"/>
+      <c r="Q182" s="4"/>
+      <c r="R182" s="4"/>
+      <c r="S182" s="4"/>
+      <c r="T182" s="4"/>
+      <c r="U182" s="4"/>
+      <c r="V182" s="4"/>
+      <c r="W182" s="4"/>
+      <c r="X182" s="4"/>
+      <c r="Y182" s="4"/>
+      <c r="Z182" s="4"/>
+    </row>
+    <row r="183" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A183" s="4"/>
+      <c r="B183" s="4"/>
+      <c r="C183" s="4"/>
+      <c r="D183" s="4"/>
+      <c r="E183" s="4"/>
+      <c r="F183" s="4"/>
+      <c r="G183" s="4"/>
+      <c r="H183" s="4"/>
+      <c r="I183" s="4"/>
+      <c r="J183" s="4"/>
+      <c r="K183" s="4"/>
+      <c r="L183" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="M183" s="4"/>
+      <c r="N183" s="4"/>
+      <c r="O183" s="4"/>
+      <c r="P183" s="4"/>
+      <c r="Q183" s="4"/>
+      <c r="R183" s="4"/>
+      <c r="S183" s="4"/>
+      <c r="T183" s="4"/>
+      <c r="U183" s="4"/>
+      <c r="V183" s="4"/>
+      <c r="W183" s="4"/>
+      <c r="X183" s="4"/>
+      <c r="Y183" s="4"/>
+      <c r="Z183" s="4"/>
+    </row>
+    <row r="184" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A184" s="4"/>
+      <c r="B184" s="4"/>
+      <c r="C184" s="4"/>
+      <c r="D184" s="4"/>
+      <c r="E184" s="4"/>
+      <c r="F184" s="4"/>
+      <c r="G184" s="4"/>
+      <c r="H184" s="4"/>
+      <c r="I184" s="4"/>
+      <c r="J184" s="4"/>
+      <c r="K184" s="4"/>
+      <c r="L184" s="1"/>
+      <c r="M184" s="4"/>
+      <c r="N184" s="4"/>
+      <c r="O184" s="4"/>
+      <c r="P184" s="4"/>
+      <c r="Q184" s="4"/>
+      <c r="R184" s="4"/>
+      <c r="S184" s="4"/>
+      <c r="T184" s="4"/>
+      <c r="U184" s="4"/>
+      <c r="V184" s="4"/>
+      <c r="W184" s="4"/>
+      <c r="X184" s="4"/>
+      <c r="Y184" s="4"/>
+      <c r="Z184" s="4"/>
+    </row>
+    <row r="185" spans="1:26" ht="27.4" x14ac:dyDescent="0.6">
+      <c r="A185" s="4"/>
+      <c r="B185" s="4"/>
+      <c r="C185" s="4"/>
+      <c r="D185" s="4"/>
+      <c r="E185" s="4"/>
+      <c r="F185" s="4"/>
+      <c r="G185" s="4"/>
+      <c r="H185" s="4"/>
+      <c r="I185" s="4"/>
+      <c r="J185" s="4"/>
+      <c r="K185" s="4"/>
+      <c r="L185" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="M185" s="4"/>
+      <c r="N185" s="4"/>
+      <c r="O185" s="4"/>
+      <c r="P185" s="4"/>
+      <c r="Q185" s="4"/>
+      <c r="R185" s="4"/>
+      <c r="S185" s="4"/>
+      <c r="T185" s="4"/>
+      <c r="U185" s="4"/>
+      <c r="V185" s="4"/>
+      <c r="W185" s="4"/>
+      <c r="X185" s="4"/>
+      <c r="Y185" s="4"/>
+      <c r="Z185" s="4"/>
+    </row>
+    <row r="186" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A186" s="4"/>
+      <c r="B186" s="4"/>
+      <c r="C186" s="4"/>
+      <c r="D186" s="4"/>
+      <c r="E186" s="4"/>
+      <c r="F186" s="4"/>
+      <c r="G186" s="4"/>
+      <c r="H186" s="4"/>
+      <c r="I186" s="4"/>
+      <c r="J186" s="4"/>
+      <c r="K186" s="4"/>
+      <c r="L186" s="1"/>
+      <c r="M186" s="4"/>
+      <c r="N186" s="4"/>
+      <c r="O186" s="4"/>
+      <c r="P186" s="4"/>
+      <c r="Q186" s="4"/>
+      <c r="R186" s="4"/>
+      <c r="S186" s="4"/>
+      <c r="T186" s="4"/>
+      <c r="U186" s="4"/>
+      <c r="V186" s="4"/>
+      <c r="W186" s="4"/>
+      <c r="X186" s="4"/>
+      <c r="Y186" s="4"/>
+      <c r="Z186" s="4"/>
+    </row>
+    <row r="187" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A187" s="4"/>
+      <c r="B187" s="4"/>
+      <c r="C187" s="4"/>
+      <c r="D187" s="4"/>
+      <c r="E187" s="4"/>
+      <c r="F187" s="4"/>
+      <c r="G187" s="4"/>
+      <c r="H187" s="4"/>
+      <c r="I187" s="4"/>
+      <c r="J187" s="4"/>
+      <c r="K187" s="4"/>
+      <c r="L187" s="1"/>
+      <c r="M187" s="4"/>
+      <c r="N187" s="4"/>
+      <c r="O187" s="4"/>
+      <c r="P187" s="4"/>
+      <c r="Q187" s="4"/>
+      <c r="R187" s="4"/>
+      <c r="S187" s="4"/>
+      <c r="T187" s="4"/>
+      <c r="U187" s="4"/>
+      <c r="V187" s="4"/>
+      <c r="W187" s="4"/>
+      <c r="X187" s="4"/>
+      <c r="Y187" s="4"/>
+      <c r="Z187" s="4"/>
+    </row>
+    <row r="188" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A188" s="4"/>
+      <c r="B188" s="4"/>
+      <c r="C188" s="4"/>
+      <c r="D188" s="4"/>
+      <c r="E188" s="4"/>
+      <c r="F188" s="4"/>
+      <c r="G188" s="4"/>
+      <c r="H188" s="4"/>
+      <c r="I188" s="4"/>
+      <c r="J188" s="4"/>
+      <c r="K188" s="4"/>
+      <c r="L188" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="M188" s="4"/>
+      <c r="N188" s="4"/>
+      <c r="O188" s="4"/>
+      <c r="P188" s="4"/>
+      <c r="Q188" s="4"/>
+      <c r="R188" s="4"/>
+      <c r="S188" s="4"/>
+      <c r="T188" s="4"/>
+      <c r="U188" s="4"/>
+      <c r="V188" s="4"/>
+      <c r="W188" s="4"/>
+      <c r="X188" s="4"/>
+      <c r="Y188" s="4"/>
+      <c r="Z188" s="4"/>
+    </row>
+    <row r="189" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A189" s="4"/>
+      <c r="B189" s="4"/>
+      <c r="C189" s="4"/>
+      <c r="D189" s="4"/>
+      <c r="E189" s="4"/>
+      <c r="F189" s="4"/>
+      <c r="G189" s="4"/>
+      <c r="H189" s="4"/>
+      <c r="I189" s="4"/>
+      <c r="J189" s="4"/>
+      <c r="K189" s="4"/>
+      <c r="L189" s="1"/>
+      <c r="M189" s="4"/>
+      <c r="N189" s="4"/>
+      <c r="O189" s="4"/>
+      <c r="P189" s="4"/>
+      <c r="Q189" s="4"/>
+      <c r="R189" s="4"/>
+      <c r="S189" s="4"/>
+      <c r="T189" s="4"/>
+      <c r="U189" s="4"/>
+      <c r="V189" s="4"/>
+      <c r="W189" s="4"/>
+      <c r="X189" s="4"/>
+      <c r="Y189" s="4"/>
+      <c r="Z189" s="4"/>
+    </row>
+    <row r="190" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A190" s="4"/>
+      <c r="B190" s="4"/>
+      <c r="C190" s="4"/>
+      <c r="D190" s="4"/>
+      <c r="E190" s="4"/>
+      <c r="F190" s="4"/>
+      <c r="G190" s="4"/>
+      <c r="H190" s="4"/>
+      <c r="I190" s="4"/>
+      <c r="J190" s="4"/>
+      <c r="K190" s="4"/>
+      <c r="L190" s="1"/>
+      <c r="M190" s="4"/>
+      <c r="N190" s="4"/>
+      <c r="O190" s="4"/>
+      <c r="P190" s="4"/>
+      <c r="Q190" s="4"/>
+      <c r="R190" s="4"/>
+      <c r="S190" s="4"/>
+      <c r="T190" s="4"/>
+      <c r="U190" s="4"/>
+      <c r="V190" s="4"/>
+      <c r="W190" s="4"/>
+      <c r="X190" s="4"/>
+      <c r="Y190" s="4"/>
+      <c r="Z190" s="4"/>
+    </row>
+    <row r="191" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A191" s="4"/>
+      <c r="B191" s="4"/>
+      <c r="C191" s="4"/>
+      <c r="D191" s="4"/>
+      <c r="E191" s="4"/>
+      <c r="F191" s="4"/>
+      <c r="G191" s="4"/>
+      <c r="H191" s="4"/>
+      <c r="I191" s="4"/>
+      <c r="J191" s="4"/>
+      <c r="K191" s="4"/>
+      <c r="L191" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="M191" s="4"/>
+      <c r="N191" s="4"/>
+      <c r="O191" s="4"/>
+      <c r="P191" s="4"/>
+      <c r="Q191" s="4"/>
+      <c r="R191" s="4"/>
+      <c r="S191" s="4"/>
+      <c r="T191" s="4"/>
+      <c r="U191" s="4"/>
+      <c r="V191" s="4"/>
+      <c r="W191" s="4"/>
+      <c r="X191" s="4"/>
+      <c r="Y191" s="4"/>
+      <c r="Z191" s="4"/>
+    </row>
+    <row r="192" spans="1:26" ht="40.5" x14ac:dyDescent="0.6">
+      <c r="A192" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="C192" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="H192" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="I192" s="2">
+        <v>9</v>
+      </c>
+      <c r="J192" s="2">
+        <v>9</v>
+      </c>
+      <c r="K192" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="L192" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="M192" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="N192" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="O192" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="P192" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="Q192" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="R192" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="S192" s="2">
+        <v>1</v>
+      </c>
+      <c r="T192" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="U192" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="V192" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="W192" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="X192" s="2"/>
+      <c r="Y192" s="2"/>
+      <c r="Z192" s="2"/>
+    </row>
+    <row r="193" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A193" s="6"/>
+      <c r="B193" s="6"/>
+      <c r="C193" s="6"/>
+      <c r="D193" s="6"/>
+      <c r="E193" s="6"/>
+      <c r="F193" s="6"/>
+      <c r="G193" s="6"/>
+      <c r="H193" s="6"/>
+      <c r="I193" s="6"/>
+      <c r="J193" s="6"/>
+      <c r="K193" s="6"/>
+      <c r="L193" s="6"/>
+      <c r="M193" s="6"/>
+      <c r="N193" s="6"/>
+      <c r="O193" s="6"/>
+      <c r="P193" s="6"/>
+      <c r="Q193" s="6"/>
+      <c r="R193" s="6"/>
+      <c r="S193" s="6"/>
+      <c r="T193" s="6"/>
+      <c r="U193" s="6"/>
+      <c r="V193" s="6"/>
+      <c r="W193" s="6"/>
+      <c r="X193" s="6"/>
+      <c r="Y193" s="6"/>
+      <c r="Z193" s="6"/>
+    </row>
+    <row r="194" spans="1:26" ht="54" x14ac:dyDescent="0.6">
+      <c r="A194" s="7" t="s">
+        <v>884</v>
+      </c>
+      <c r="B194" s="7" t="s">
+        <v>885</v>
+      </c>
+      <c r="C194" s="7">
+        <v>2022</v>
+      </c>
+      <c r="D194" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E194" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F194" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="G194" s="7" t="s">
+        <v>886</v>
+      </c>
+      <c r="H194" s="7" t="s">
+        <v>887</v>
+      </c>
+      <c r="I194" s="7">
+        <v>3</v>
+      </c>
+      <c r="J194" s="7">
+        <v>6</v>
+      </c>
+      <c r="K194" s="7"/>
+      <c r="L194" s="7" t="s">
+        <v>888</v>
+      </c>
+      <c r="M194" s="7" t="s">
+        <v>889</v>
+      </c>
+      <c r="N194" s="7" t="s">
+        <v>890</v>
+      </c>
+      <c r="O194" s="7" t="s">
+        <v>891</v>
+      </c>
+      <c r="P194" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="Q194" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="R194" s="7" t="s">
+        <v>894</v>
+      </c>
+      <c r="S194" s="7">
+        <v>2</v>
+      </c>
+      <c r="T194" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="U194" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="V194" s="7">
+        <v>-0.05</v>
+      </c>
+      <c r="W194" s="7" t="s">
+        <v>896</v>
+      </c>
+      <c r="X194" s="7">
+        <v>-0.06</v>
+      </c>
+      <c r="Y194" s="7">
+        <v>-0.03</v>
+      </c>
+      <c r="Z194" s="8">
+        <v>2.3600000000000001E-11</v>
+      </c>
+    </row>
+    <row r="195" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A195" s="9" t="s">
+        <v>884</v>
+      </c>
+      <c r="B195" s="9" t="s">
+        <v>885</v>
+      </c>
+      <c r="C195" s="9">
+        <v>2022</v>
+      </c>
+      <c r="D195" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="E195" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F195" s="9" t="s">
+        <v>844</v>
+      </c>
+      <c r="G195" s="9" t="s">
+        <v>886</v>
+      </c>
+      <c r="H195" s="9" t="s">
+        <v>887</v>
+      </c>
+      <c r="I195" s="9">
+        <v>3</v>
+      </c>
+      <c r="J195" s="9">
+        <v>6</v>
+      </c>
+      <c r="K195" s="9" t="s">
+        <v>833</v>
+      </c>
+      <c r="L195" s="6" t="s">
+        <v>897</v>
+      </c>
+      <c r="M195" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="N195" s="9" t="s">
+        <v>890</v>
+      </c>
+      <c r="O195" s="9" t="s">
+        <v>891</v>
+      </c>
+      <c r="P195" s="9" t="s">
+        <v>892</v>
+      </c>
+      <c r="Q195" s="9" t="s">
+        <v>893</v>
+      </c>
+      <c r="R195" s="9" t="s">
+        <v>894</v>
+      </c>
+      <c r="S195" s="9">
+        <v>2</v>
+      </c>
+      <c r="T195" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="U195" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="V195" s="9">
+        <v>-0.05</v>
+      </c>
+      <c r="W195" s="9" t="s">
+        <v>896</v>
+      </c>
+      <c r="X195" s="9">
+        <v>-0.06</v>
+      </c>
+      <c r="Y195" s="9">
+        <v>-0.03</v>
+      </c>
+      <c r="Z195" s="9" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="196" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A196" s="9"/>
+      <c r="B196" s="9"/>
+      <c r="C196" s="9"/>
+      <c r="D196" s="9"/>
+      <c r="E196" s="9"/>
+      <c r="F196" s="9"/>
+      <c r="G196" s="9"/>
+      <c r="H196" s="9"/>
+      <c r="I196" s="9"/>
+      <c r="J196" s="9"/>
+      <c r="K196" s="9"/>
+      <c r="L196" s="5"/>
+      <c r="M196" s="9"/>
+      <c r="N196" s="9"/>
+      <c r="O196" s="9"/>
+      <c r="P196" s="9"/>
+      <c r="Q196" s="9"/>
+      <c r="R196" s="9"/>
+      <c r="S196" s="9"/>
+      <c r="T196" s="9"/>
+      <c r="U196" s="9"/>
+      <c r="V196" s="9"/>
+      <c r="W196" s="9"/>
+      <c r="X196" s="9"/>
+      <c r="Y196" s="9"/>
+      <c r="Z196" s="9"/>
+    </row>
+    <row r="197" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A197" s="9"/>
+      <c r="B197" s="9"/>
+      <c r="C197" s="9"/>
+      <c r="D197" s="9"/>
+      <c r="E197" s="9"/>
+      <c r="F197" s="9"/>
+      <c r="G197" s="9"/>
+      <c r="H197" s="9"/>
+      <c r="I197" s="9"/>
+      <c r="J197" s="9"/>
+      <c r="K197" s="9"/>
+      <c r="L197" s="6" t="s">
+        <v>898</v>
+      </c>
+      <c r="M197" s="9"/>
+      <c r="N197" s="9"/>
+      <c r="O197" s="9"/>
+      <c r="P197" s="9"/>
+      <c r="Q197" s="9"/>
+      <c r="R197" s="9"/>
+      <c r="S197" s="9"/>
+      <c r="T197" s="9"/>
+      <c r="U197" s="9"/>
+      <c r="V197" s="9"/>
+      <c r="W197" s="9"/>
+      <c r="X197" s="9"/>
+      <c r="Y197" s="9"/>
+      <c r="Z197" s="9"/>
+    </row>
+    <row r="198" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A198" s="9"/>
+      <c r="B198" s="9"/>
+      <c r="C198" s="9"/>
+      <c r="D198" s="9"/>
+      <c r="E198" s="9"/>
+      <c r="F198" s="9"/>
+      <c r="G198" s="9"/>
+      <c r="H198" s="9"/>
+      <c r="I198" s="9"/>
+      <c r="J198" s="9"/>
+      <c r="K198" s="9"/>
+      <c r="L198" s="5"/>
+      <c r="M198" s="9"/>
+      <c r="N198" s="9"/>
+      <c r="O198" s="9"/>
+      <c r="P198" s="9"/>
+      <c r="Q198" s="9"/>
+      <c r="R198" s="9"/>
+      <c r="S198" s="9"/>
+      <c r="T198" s="9"/>
+      <c r="U198" s="9"/>
+      <c r="V198" s="9"/>
+      <c r="W198" s="9"/>
+      <c r="X198" s="9"/>
+      <c r="Y198" s="9"/>
+      <c r="Z198" s="9"/>
+    </row>
+    <row r="199" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A199" s="9"/>
+      <c r="B199" s="9"/>
+      <c r="C199" s="9"/>
+      <c r="D199" s="9"/>
+      <c r="E199" s="9"/>
+      <c r="F199" s="9"/>
+      <c r="G199" s="9"/>
+      <c r="H199" s="9"/>
+      <c r="I199" s="9"/>
+      <c r="J199" s="9"/>
+      <c r="K199" s="9"/>
+      <c r="L199" s="6" t="s">
+        <v>899</v>
+      </c>
+      <c r="M199" s="9"/>
+      <c r="N199" s="9"/>
+      <c r="O199" s="9"/>
+      <c r="P199" s="9"/>
+      <c r="Q199" s="9"/>
+      <c r="R199" s="9"/>
+      <c r="S199" s="9"/>
+      <c r="T199" s="9"/>
+      <c r="U199" s="9"/>
+      <c r="V199" s="9"/>
+      <c r="W199" s="9"/>
+      <c r="X199" s="9"/>
+      <c r="Y199" s="9"/>
+      <c r="Z199" s="9"/>
+    </row>
+    <row r="200" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A200" s="9"/>
+      <c r="B200" s="9"/>
+      <c r="C200" s="9"/>
+      <c r="D200" s="9"/>
+      <c r="E200" s="9"/>
+      <c r="F200" s="9"/>
+      <c r="G200" s="9"/>
+      <c r="H200" s="9"/>
+      <c r="I200" s="9"/>
+      <c r="J200" s="9"/>
+      <c r="K200" s="9"/>
+      <c r="L200" s="5"/>
+      <c r="M200" s="9"/>
+      <c r="N200" s="9"/>
+      <c r="O200" s="9"/>
+      <c r="P200" s="9"/>
+      <c r="Q200" s="9"/>
+      <c r="R200" s="9"/>
+      <c r="S200" s="9"/>
+      <c r="T200" s="9"/>
+      <c r="U200" s="9"/>
+      <c r="V200" s="9"/>
+      <c r="W200" s="9"/>
+      <c r="X200" s="9"/>
+      <c r="Y200" s="9"/>
+      <c r="Z200" s="9"/>
+    </row>
+    <row r="201" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A201" s="9"/>
+      <c r="B201" s="9"/>
+      <c r="C201" s="9"/>
+      <c r="D201" s="9"/>
+      <c r="E201" s="9"/>
+      <c r="F201" s="9"/>
+      <c r="G201" s="9"/>
+      <c r="H201" s="9"/>
+      <c r="I201" s="9"/>
+      <c r="J201" s="9"/>
+      <c r="K201" s="9"/>
+      <c r="L201" s="6" t="s">
+        <v>900</v>
+      </c>
+      <c r="M201" s="9"/>
+      <c r="N201" s="9"/>
+      <c r="O201" s="9"/>
+      <c r="P201" s="9"/>
+      <c r="Q201" s="9"/>
+      <c r="R201" s="9"/>
+      <c r="S201" s="9"/>
+      <c r="T201" s="9"/>
+      <c r="U201" s="9"/>
+      <c r="V201" s="9"/>
+      <c r="W201" s="9"/>
+      <c r="X201" s="9"/>
+      <c r="Y201" s="9"/>
+      <c r="Z201" s="9"/>
+    </row>
+    <row r="202" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A202" s="9"/>
+      <c r="B202" s="9"/>
+      <c r="C202" s="9"/>
+      <c r="D202" s="9"/>
+      <c r="E202" s="9"/>
+      <c r="F202" s="9"/>
+      <c r="G202" s="9"/>
+      <c r="H202" s="9"/>
+      <c r="I202" s="9"/>
+      <c r="J202" s="9"/>
+      <c r="K202" s="9"/>
+      <c r="L202" s="5"/>
+      <c r="M202" s="9"/>
+      <c r="N202" s="9"/>
+      <c r="O202" s="9"/>
+      <c r="P202" s="9"/>
+      <c r="Q202" s="9"/>
+      <c r="R202" s="9"/>
+      <c r="S202" s="9"/>
+      <c r="T202" s="9"/>
+      <c r="U202" s="9"/>
+      <c r="V202" s="9"/>
+      <c r="W202" s="9"/>
+      <c r="X202" s="9"/>
+      <c r="Y202" s="9"/>
+      <c r="Z202" s="9"/>
+    </row>
+    <row r="203" spans="1:26" ht="27.4" x14ac:dyDescent="0.6">
+      <c r="A203" s="9"/>
+      <c r="B203" s="9"/>
+      <c r="C203" s="9"/>
+      <c r="D203" s="9"/>
+      <c r="E203" s="9"/>
+      <c r="F203" s="9"/>
+      <c r="G203" s="9"/>
+      <c r="H203" s="9"/>
+      <c r="I203" s="9"/>
+      <c r="J203" s="9"/>
+      <c r="K203" s="9"/>
+      <c r="L203" s="6" t="s">
+        <v>901</v>
+      </c>
+      <c r="M203" s="9"/>
+      <c r="N203" s="9"/>
+      <c r="O203" s="9"/>
+      <c r="P203" s="9"/>
+      <c r="Q203" s="9"/>
+      <c r="R203" s="9"/>
+      <c r="S203" s="9"/>
+      <c r="T203" s="9"/>
+      <c r="U203" s="9"/>
+      <c r="V203" s="9"/>
+      <c r="W203" s="9"/>
+      <c r="X203" s="9"/>
+      <c r="Y203" s="9"/>
+      <c r="Z203" s="9"/>
+    </row>
+    <row r="204" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A204" s="9"/>
+      <c r="B204" s="9"/>
+      <c r="C204" s="9"/>
+      <c r="D204" s="9"/>
+      <c r="E204" s="9"/>
+      <c r="F204" s="9"/>
+      <c r="G204" s="9"/>
+      <c r="H204" s="9"/>
+      <c r="I204" s="9"/>
+      <c r="J204" s="9"/>
+      <c r="K204" s="9"/>
+      <c r="L204" s="5"/>
+      <c r="M204" s="9"/>
+      <c r="N204" s="9"/>
+      <c r="O204" s="9"/>
+      <c r="P204" s="9"/>
+      <c r="Q204" s="9"/>
+      <c r="R204" s="9"/>
+      <c r="S204" s="9"/>
+      <c r="T204" s="9"/>
+      <c r="U204" s="9"/>
+      <c r="V204" s="9"/>
+      <c r="W204" s="9"/>
+      <c r="X204" s="9"/>
+      <c r="Y204" s="9"/>
+      <c r="Z204" s="9"/>
+    </row>
+    <row r="205" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A205" s="9"/>
+      <c r="B205" s="9"/>
+      <c r="C205" s="9"/>
+      <c r="D205" s="9"/>
+      <c r="E205" s="9"/>
+      <c r="F205" s="9"/>
+      <c r="G205" s="9"/>
+      <c r="H205" s="9"/>
+      <c r="I205" s="9"/>
+      <c r="J205" s="9"/>
+      <c r="K205" s="9"/>
+      <c r="L205" s="5"/>
+      <c r="M205" s="9"/>
+      <c r="N205" s="9"/>
+      <c r="O205" s="9"/>
+      <c r="P205" s="9"/>
+      <c r="Q205" s="9"/>
+      <c r="R205" s="9"/>
+      <c r="S205" s="9"/>
+      <c r="T205" s="9"/>
+      <c r="U205" s="9"/>
+      <c r="V205" s="9"/>
+      <c r="W205" s="9"/>
+      <c r="X205" s="9"/>
+      <c r="Y205" s="9"/>
+      <c r="Z205" s="9"/>
+    </row>
+    <row r="206" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A206" s="9"/>
+      <c r="B206" s="9"/>
+      <c r="C206" s="9"/>
+      <c r="D206" s="9"/>
+      <c r="E206" s="9"/>
+      <c r="F206" s="9"/>
+      <c r="G206" s="9"/>
+      <c r="H206" s="9"/>
+      <c r="I206" s="9"/>
+      <c r="J206" s="9"/>
+      <c r="K206" s="9"/>
+      <c r="L206" s="6" t="s">
+        <v>902</v>
+      </c>
+      <c r="M206" s="9"/>
+      <c r="N206" s="9"/>
+      <c r="O206" s="9"/>
+      <c r="P206" s="9"/>
+      <c r="Q206" s="9"/>
+      <c r="R206" s="9"/>
+      <c r="S206" s="9"/>
+      <c r="T206" s="9"/>
+      <c r="U206" s="9"/>
+      <c r="V206" s="9"/>
+      <c r="W206" s="9"/>
+      <c r="X206" s="9"/>
+      <c r="Y206" s="9"/>
+      <c r="Z206" s="9"/>
+    </row>
+    <row r="207" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A207" s="9"/>
+      <c r="B207" s="9"/>
+      <c r="C207" s="9"/>
+      <c r="D207" s="9"/>
+      <c r="E207" s="9"/>
+      <c r="F207" s="9"/>
+      <c r="G207" s="9"/>
+      <c r="H207" s="9"/>
+      <c r="I207" s="9"/>
+      <c r="J207" s="9"/>
+      <c r="K207" s="9"/>
+      <c r="L207" s="5"/>
+      <c r="M207" s="9"/>
+      <c r="N207" s="9"/>
+      <c r="O207" s="9"/>
+      <c r="P207" s="9"/>
+      <c r="Q207" s="9"/>
+      <c r="R207" s="9"/>
+      <c r="S207" s="9"/>
+      <c r="T207" s="9"/>
+      <c r="U207" s="9"/>
+      <c r="V207" s="9"/>
+      <c r="W207" s="9"/>
+      <c r="X207" s="9"/>
+      <c r="Y207" s="9"/>
+      <c r="Z207" s="9"/>
+    </row>
+    <row r="208" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A208" s="9"/>
+      <c r="B208" s="9"/>
+      <c r="C208" s="9"/>
+      <c r="D208" s="9"/>
+      <c r="E208" s="9"/>
+      <c r="F208" s="9"/>
+      <c r="G208" s="9"/>
+      <c r="H208" s="9"/>
+      <c r="I208" s="9"/>
+      <c r="J208" s="9"/>
+      <c r="K208" s="9"/>
+      <c r="L208" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="M208" s="9"/>
+      <c r="N208" s="9"/>
+      <c r="O208" s="9"/>
+      <c r="P208" s="9"/>
+      <c r="Q208" s="9"/>
+      <c r="R208" s="9"/>
+      <c r="S208" s="9"/>
+      <c r="T208" s="9"/>
+      <c r="U208" s="9"/>
+      <c r="V208" s="9"/>
+      <c r="W208" s="9"/>
+      <c r="X208" s="9"/>
+      <c r="Y208" s="9"/>
+      <c r="Z208" s="9"/>
+    </row>
+    <row r="209" spans="1:26" ht="40.5" x14ac:dyDescent="0.6">
+      <c r="A209" s="7" t="s">
+        <v>884</v>
+      </c>
+      <c r="B209" s="7" t="s">
+        <v>885</v>
+      </c>
+      <c r="C209" s="7">
+        <v>2022</v>
+      </c>
+      <c r="D209" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E209" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F209" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="G209" s="7" t="s">
+        <v>886</v>
+      </c>
+      <c r="H209" s="7" t="s">
+        <v>887</v>
+      </c>
+      <c r="I209" s="7">
+        <v>3</v>
+      </c>
+      <c r="J209" s="7">
+        <v>6</v>
+      </c>
+      <c r="K209" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="L209" s="7" t="s">
+        <v>905</v>
+      </c>
+      <c r="M209" s="7" t="s">
+        <v>889</v>
+      </c>
+      <c r="N209" s="7" t="s">
+        <v>890</v>
+      </c>
+      <c r="O209" s="7" t="s">
+        <v>891</v>
+      </c>
+      <c r="P209" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="Q209" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="R209" s="7" t="s">
+        <v>894</v>
+      </c>
+      <c r="S209" s="7">
+        <v>2</v>
+      </c>
+      <c r="T209" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="U209" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="V209" s="7">
+        <v>-0.05</v>
+      </c>
+      <c r="W209" s="7" t="s">
+        <v>896</v>
+      </c>
+      <c r="X209" s="7"/>
+      <c r="Y209" s="7"/>
+      <c r="Z209" s="7" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="210" spans="1:26" ht="54" x14ac:dyDescent="0.6">
+      <c r="A210" s="7" t="s">
+        <v>884</v>
+      </c>
+      <c r="B210" s="7" t="s">
+        <v>885</v>
+      </c>
+      <c r="C210" s="7">
+        <v>2022</v>
+      </c>
+      <c r="D210" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E210" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F210" s="7" t="s">
+        <v>855</v>
+      </c>
+      <c r="G210" s="7" t="s">
+        <v>886</v>
+      </c>
+      <c r="H210" s="7" t="s">
+        <v>906</v>
+      </c>
+      <c r="I210" s="7">
+        <v>4</v>
+      </c>
+      <c r="J210" s="7">
+        <v>6</v>
+      </c>
+      <c r="K210" s="7"/>
+      <c r="L210" s="7" t="s">
+        <v>907</v>
+      </c>
+      <c r="M210" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="N210" s="7" t="s">
+        <v>890</v>
+      </c>
+      <c r="O210" s="7" t="s">
+        <v>891</v>
+      </c>
+      <c r="P210" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="Q210" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="R210" s="7" t="s">
+        <v>909</v>
+      </c>
+      <c r="S210" s="7">
+        <v>1</v>
+      </c>
+      <c r="T210" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="U210" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="V210" s="7">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="W210" s="7" t="s">
+        <v>896</v>
+      </c>
+      <c r="X210" s="7">
+        <v>-0.11</v>
+      </c>
+      <c r="Y210" s="7">
+        <v>-0.03</v>
+      </c>
+      <c r="Z210" s="7">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A211" s="9" t="s">
+        <v>884</v>
+      </c>
+      <c r="B211" s="9" t="s">
+        <v>885</v>
+      </c>
+      <c r="C211" s="9">
+        <v>2022</v>
+      </c>
+      <c r="D211" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="E211" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F211" s="9" t="s">
+        <v>861</v>
+      </c>
+      <c r="G211" s="9" t="s">
+        <v>886</v>
+      </c>
+      <c r="H211" s="9" t="s">
+        <v>906</v>
+      </c>
+      <c r="I211" s="9">
+        <v>4</v>
+      </c>
+      <c r="J211" s="9">
+        <v>6</v>
+      </c>
+      <c r="K211" s="9" t="s">
+        <v>855</v>
+      </c>
+      <c r="L211" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="M211" s="9" t="s">
+        <v>908</v>
+      </c>
+      <c r="N211" s="9" t="s">
+        <v>890</v>
+      </c>
+      <c r="O211" s="9" t="s">
+        <v>891</v>
+      </c>
+      <c r="P211" s="9" t="s">
+        <v>892</v>
+      </c>
+      <c r="Q211" s="9" t="s">
+        <v>893</v>
+      </c>
+      <c r="R211" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="S211" s="9">
+        <v>1</v>
+      </c>
+      <c r="T211" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="U211" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="V211" s="9">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="W211" s="9" t="s">
+        <v>896</v>
+      </c>
+      <c r="X211" s="9">
+        <v>-0.11</v>
+      </c>
+      <c r="Y211" s="9">
+        <v>-0.03</v>
+      </c>
+      <c r="Z211" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A212" s="9"/>
+      <c r="B212" s="9"/>
+      <c r="C212" s="9"/>
+      <c r="D212" s="9"/>
+      <c r="E212" s="9"/>
+      <c r="F212" s="9"/>
+      <c r="G212" s="9"/>
+      <c r="H212" s="9"/>
+      <c r="I212" s="9"/>
+      <c r="J212" s="9"/>
+      <c r="K212" s="9"/>
+      <c r="L212" s="5"/>
+      <c r="M212" s="9"/>
+      <c r="N212" s="9"/>
+      <c r="O212" s="9"/>
+      <c r="P212" s="9"/>
+      <c r="Q212" s="9"/>
+      <c r="R212" s="9"/>
+      <c r="S212" s="9"/>
+      <c r="T212" s="9"/>
+      <c r="U212" s="9"/>
+      <c r="V212" s="9"/>
+      <c r="W212" s="9"/>
+      <c r="X212" s="9"/>
+      <c r="Y212" s="9"/>
+      <c r="Z212" s="9"/>
+    </row>
+    <row r="213" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A213" s="9"/>
+      <c r="B213" s="9"/>
+      <c r="C213" s="9"/>
+      <c r="D213" s="9"/>
+      <c r="E213" s="9"/>
+      <c r="F213" s="9"/>
+      <c r="G213" s="9"/>
+      <c r="H213" s="9"/>
+      <c r="I213" s="9"/>
+      <c r="J213" s="9"/>
+      <c r="K213" s="9"/>
+      <c r="L213" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="M213" s="9"/>
+      <c r="N213" s="9"/>
+      <c r="O213" s="9"/>
+      <c r="P213" s="9"/>
+      <c r="Q213" s="9"/>
+      <c r="R213" s="9"/>
+      <c r="S213" s="9"/>
+      <c r="T213" s="9"/>
+      <c r="U213" s="9"/>
+      <c r="V213" s="9"/>
+      <c r="W213" s="9"/>
+      <c r="X213" s="9"/>
+      <c r="Y213" s="9"/>
+      <c r="Z213" s="9"/>
+    </row>
+    <row r="214" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A214" s="9"/>
+      <c r="B214" s="9"/>
+      <c r="C214" s="9"/>
+      <c r="D214" s="9"/>
+      <c r="E214" s="9"/>
+      <c r="F214" s="9"/>
+      <c r="G214" s="9"/>
+      <c r="H214" s="9"/>
+      <c r="I214" s="9"/>
+      <c r="J214" s="9"/>
+      <c r="K214" s="9"/>
+      <c r="L214" s="5"/>
+      <c r="M214" s="9"/>
+      <c r="N214" s="9"/>
+      <c r="O214" s="9"/>
+      <c r="P214" s="9"/>
+      <c r="Q214" s="9"/>
+      <c r="R214" s="9"/>
+      <c r="S214" s="9"/>
+      <c r="T214" s="9"/>
+      <c r="U214" s="9"/>
+      <c r="V214" s="9"/>
+      <c r="W214" s="9"/>
+      <c r="X214" s="9"/>
+      <c r="Y214" s="9"/>
+      <c r="Z214" s="9"/>
+    </row>
+    <row r="215" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A215" s="9"/>
+      <c r="B215" s="9"/>
+      <c r="C215" s="9"/>
+      <c r="D215" s="9"/>
+      <c r="E215" s="9"/>
+      <c r="F215" s="9"/>
+      <c r="G215" s="9"/>
+      <c r="H215" s="9"/>
+      <c r="I215" s="9"/>
+      <c r="J215" s="9"/>
+      <c r="K215" s="9"/>
+      <c r="L215" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="M215" s="9"/>
+      <c r="N215" s="9"/>
+      <c r="O215" s="9"/>
+      <c r="P215" s="9"/>
+      <c r="Q215" s="9"/>
+      <c r="R215" s="9"/>
+      <c r="S215" s="9"/>
+      <c r="T215" s="9"/>
+      <c r="U215" s="9"/>
+      <c r="V215" s="9"/>
+      <c r="W215" s="9"/>
+      <c r="X215" s="9"/>
+      <c r="Y215" s="9"/>
+      <c r="Z215" s="9"/>
+    </row>
+    <row r="216" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A216" s="9"/>
+      <c r="B216" s="9"/>
+      <c r="C216" s="9"/>
+      <c r="D216" s="9"/>
+      <c r="E216" s="9"/>
+      <c r="F216" s="9"/>
+      <c r="G216" s="9"/>
+      <c r="H216" s="9"/>
+      <c r="I216" s="9"/>
+      <c r="J216" s="9"/>
+      <c r="K216" s="9"/>
+      <c r="L216" s="5"/>
+      <c r="M216" s="9"/>
+      <c r="N216" s="9"/>
+      <c r="O216" s="9"/>
+      <c r="P216" s="9"/>
+      <c r="Q216" s="9"/>
+      <c r="R216" s="9"/>
+      <c r="S216" s="9"/>
+      <c r="T216" s="9"/>
+      <c r="U216" s="9"/>
+      <c r="V216" s="9"/>
+      <c r="W216" s="9"/>
+      <c r="X216" s="9"/>
+      <c r="Y216" s="9"/>
+      <c r="Z216" s="9"/>
+    </row>
+    <row r="217" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A217" s="9"/>
+      <c r="B217" s="9"/>
+      <c r="C217" s="9"/>
+      <c r="D217" s="9"/>
+      <c r="E217" s="9"/>
+      <c r="F217" s="9"/>
+      <c r="G217" s="9"/>
+      <c r="H217" s="9"/>
+      <c r="I217" s="9"/>
+      <c r="J217" s="9"/>
+      <c r="K217" s="9"/>
+      <c r="L217" s="6" t="s">
+        <v>900</v>
+      </c>
+      <c r="M217" s="9"/>
+      <c r="N217" s="9"/>
+      <c r="O217" s="9"/>
+      <c r="P217" s="9"/>
+      <c r="Q217" s="9"/>
+      <c r="R217" s="9"/>
+      <c r="S217" s="9"/>
+      <c r="T217" s="9"/>
+      <c r="U217" s="9"/>
+      <c r="V217" s="9"/>
+      <c r="W217" s="9"/>
+      <c r="X217" s="9"/>
+      <c r="Y217" s="9"/>
+      <c r="Z217" s="9"/>
+    </row>
+    <row r="218" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A218" s="9"/>
+      <c r="B218" s="9"/>
+      <c r="C218" s="9"/>
+      <c r="D218" s="9"/>
+      <c r="E218" s="9"/>
+      <c r="F218" s="9"/>
+      <c r="G218" s="9"/>
+      <c r="H218" s="9"/>
+      <c r="I218" s="9"/>
+      <c r="J218" s="9"/>
+      <c r="K218" s="9"/>
+      <c r="L218" s="5"/>
+      <c r="M218" s="9"/>
+      <c r="N218" s="9"/>
+      <c r="O218" s="9"/>
+      <c r="P218" s="9"/>
+      <c r="Q218" s="9"/>
+      <c r="R218" s="9"/>
+      <c r="S218" s="9"/>
+      <c r="T218" s="9"/>
+      <c r="U218" s="9"/>
+      <c r="V218" s="9"/>
+      <c r="W218" s="9"/>
+      <c r="X218" s="9"/>
+      <c r="Y218" s="9"/>
+      <c r="Z218" s="9"/>
+    </row>
+    <row r="219" spans="1:26" ht="27.4" x14ac:dyDescent="0.6">
+      <c r="A219" s="9"/>
+      <c r="B219" s="9"/>
+      <c r="C219" s="9"/>
+      <c r="D219" s="9"/>
+      <c r="E219" s="9"/>
+      <c r="F219" s="9"/>
+      <c r="G219" s="9"/>
+      <c r="H219" s="9"/>
+      <c r="I219" s="9"/>
+      <c r="J219" s="9"/>
+      <c r="K219" s="9"/>
+      <c r="L219" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="M219" s="9"/>
+      <c r="N219" s="9"/>
+      <c r="O219" s="9"/>
+      <c r="P219" s="9"/>
+      <c r="Q219" s="9"/>
+      <c r="R219" s="9"/>
+      <c r="S219" s="9"/>
+      <c r="T219" s="9"/>
+      <c r="U219" s="9"/>
+      <c r="V219" s="9"/>
+      <c r="W219" s="9"/>
+      <c r="X219" s="9"/>
+      <c r="Y219" s="9"/>
+      <c r="Z219" s="9"/>
+    </row>
+    <row r="220" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A220" s="9"/>
+      <c r="B220" s="9"/>
+      <c r="C220" s="9"/>
+      <c r="D220" s="9"/>
+      <c r="E220" s="9"/>
+      <c r="F220" s="9"/>
+      <c r="G220" s="9"/>
+      <c r="H220" s="9"/>
+      <c r="I220" s="9"/>
+      <c r="J220" s="9"/>
+      <c r="K220" s="9"/>
+      <c r="L220" s="5"/>
+      <c r="M220" s="9"/>
+      <c r="N220" s="9"/>
+      <c r="O220" s="9"/>
+      <c r="P220" s="9"/>
+      <c r="Q220" s="9"/>
+      <c r="R220" s="9"/>
+      <c r="S220" s="9"/>
+      <c r="T220" s="9"/>
+      <c r="U220" s="9"/>
+      <c r="V220" s="9"/>
+      <c r="W220" s="9"/>
+      <c r="X220" s="9"/>
+      <c r="Y220" s="9"/>
+      <c r="Z220" s="9"/>
+    </row>
+    <row r="221" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A221" s="9"/>
+      <c r="B221" s="9"/>
+      <c r="C221" s="9"/>
+      <c r="D221" s="9"/>
+      <c r="E221" s="9"/>
+      <c r="F221" s="9"/>
+      <c r="G221" s="9"/>
+      <c r="H221" s="9"/>
+      <c r="I221" s="9"/>
+      <c r="J221" s="9"/>
+      <c r="K221" s="9"/>
+      <c r="L221" s="5"/>
+      <c r="M221" s="9"/>
+      <c r="N221" s="9"/>
+      <c r="O221" s="9"/>
+      <c r="P221" s="9"/>
+      <c r="Q221" s="9"/>
+      <c r="R221" s="9"/>
+      <c r="S221" s="9"/>
+      <c r="T221" s="9"/>
+      <c r="U221" s="9"/>
+      <c r="V221" s="9"/>
+      <c r="W221" s="9"/>
+      <c r="X221" s="9"/>
+      <c r="Y221" s="9"/>
+      <c r="Z221" s="9"/>
+    </row>
+    <row r="222" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A222" s="9"/>
+      <c r="B222" s="9"/>
+      <c r="C222" s="9"/>
+      <c r="D222" s="9"/>
+      <c r="E222" s="9"/>
+      <c r="F222" s="9"/>
+      <c r="G222" s="9"/>
+      <c r="H222" s="9"/>
+      <c r="I222" s="9"/>
+      <c r="J222" s="9"/>
+      <c r="K222" s="9"/>
+      <c r="L222" s="6" t="s">
+        <v>914</v>
+      </c>
+      <c r="M222" s="9"/>
+      <c r="N222" s="9"/>
+      <c r="O222" s="9"/>
+      <c r="P222" s="9"/>
+      <c r="Q222" s="9"/>
+      <c r="R222" s="9"/>
+      <c r="S222" s="9"/>
+      <c r="T222" s="9"/>
+      <c r="U222" s="9"/>
+      <c r="V222" s="9"/>
+      <c r="W222" s="9"/>
+      <c r="X222" s="9"/>
+      <c r="Y222" s="9"/>
+      <c r="Z222" s="9"/>
+    </row>
+    <row r="223" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A223" s="9"/>
+      <c r="B223" s="9"/>
+      <c r="C223" s="9"/>
+      <c r="D223" s="9"/>
+      <c r="E223" s="9"/>
+      <c r="F223" s="9"/>
+      <c r="G223" s="9"/>
+      <c r="H223" s="9"/>
+      <c r="I223" s="9"/>
+      <c r="J223" s="9"/>
+      <c r="K223" s="9"/>
+      <c r="L223" s="5"/>
+      <c r="M223" s="9"/>
+      <c r="N223" s="9"/>
+      <c r="O223" s="9"/>
+      <c r="P223" s="9"/>
+      <c r="Q223" s="9"/>
+      <c r="R223" s="9"/>
+      <c r="S223" s="9"/>
+      <c r="T223" s="9"/>
+      <c r="U223" s="9"/>
+      <c r="V223" s="9"/>
+      <c r="W223" s="9"/>
+      <c r="X223" s="9"/>
+      <c r="Y223" s="9"/>
+      <c r="Z223" s="9"/>
+    </row>
+    <row r="224" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A224" s="9"/>
+      <c r="B224" s="9"/>
+      <c r="C224" s="9"/>
+      <c r="D224" s="9"/>
+      <c r="E224" s="9"/>
+      <c r="F224" s="9"/>
+      <c r="G224" s="9"/>
+      <c r="H224" s="9"/>
+      <c r="I224" s="9"/>
+      <c r="J224" s="9"/>
+      <c r="K224" s="9"/>
+      <c r="L224" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="M224" s="9"/>
+      <c r="N224" s="9"/>
+      <c r="O224" s="9"/>
+      <c r="P224" s="9"/>
+      <c r="Q224" s="9"/>
+      <c r="R224" s="9"/>
+      <c r="S224" s="9"/>
+      <c r="T224" s="9"/>
+      <c r="U224" s="9"/>
+      <c r="V224" s="9"/>
+      <c r="W224" s="9"/>
+      <c r="X224" s="9"/>
+      <c r="Y224" s="9"/>
+      <c r="Z224" s="9"/>
+    </row>
+    <row r="225" spans="1:26" ht="40.5" x14ac:dyDescent="0.6">
+      <c r="A225" s="7" t="s">
+        <v>884</v>
+      </c>
+      <c r="B225" s="7" t="s">
+        <v>885</v>
+      </c>
+      <c r="C225" s="7">
+        <v>2022</v>
+      </c>
+      <c r="D225" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E225" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F225" s="7" t="s">
+        <v>868</v>
+      </c>
+      <c r="G225" s="7" t="s">
+        <v>886</v>
+      </c>
+      <c r="H225" s="7" t="s">
+        <v>906</v>
+      </c>
+      <c r="I225" s="7">
+        <v>4</v>
+      </c>
+      <c r="J225" s="7">
+        <v>6</v>
+      </c>
+      <c r="K225" s="7" t="s">
+        <v>855</v>
+      </c>
+      <c r="L225" s="7" t="s">
+        <v>916</v>
+      </c>
+      <c r="M225" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="N225" s="7" t="s">
+        <v>890</v>
+      </c>
+      <c r="O225" s="7" t="s">
+        <v>891</v>
+      </c>
+      <c r="P225" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="Q225" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="R225" s="7" t="s">
+        <v>909</v>
+      </c>
+      <c r="S225" s="7">
+        <v>1</v>
+      </c>
+      <c r="T225" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="U225" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="V225" s="7">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="W225" s="7" t="s">
+        <v>896</v>
+      </c>
+      <c r="X225" s="7"/>
+      <c r="Y225" s="7"/>
+      <c r="Z225" s="7">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:26" ht="54" x14ac:dyDescent="0.6">
+      <c r="A226" s="7" t="s">
+        <v>884</v>
+      </c>
+      <c r="B226" s="7" t="s">
+        <v>885</v>
+      </c>
+      <c r="C226" s="7">
+        <v>2022</v>
+      </c>
+      <c r="D226" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E226" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F226" s="7" t="s">
+        <v>870</v>
+      </c>
+      <c r="G226" s="7" t="s">
+        <v>886</v>
+      </c>
+      <c r="H226" s="7" t="s">
+        <v>917</v>
+      </c>
+      <c r="I226" s="7">
+        <v>4</v>
+      </c>
+      <c r="J226" s="7">
+        <v>5</v>
+      </c>
+      <c r="K226" s="7"/>
+      <c r="L226" s="7" t="s">
+        <v>918</v>
+      </c>
+      <c r="M226" s="7" t="s">
+        <v>919</v>
+      </c>
+      <c r="N226" s="7" t="s">
+        <v>890</v>
+      </c>
+      <c r="O226" s="7" t="s">
+        <v>891</v>
+      </c>
+      <c r="P226" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="Q226" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="R226" s="7" t="s">
+        <v>909</v>
+      </c>
+      <c r="S226" s="7">
+        <v>1</v>
+      </c>
+      <c r="T226" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="U226" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="V226" s="7">
+        <v>-0.17</v>
+      </c>
+      <c r="W226" s="7" t="s">
+        <v>920</v>
+      </c>
+      <c r="X226" s="7">
+        <v>-0.3</v>
+      </c>
+      <c r="Y226" s="7">
+        <v>-0.04</v>
+      </c>
+      <c r="Z226" s="7">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A227" s="9" t="s">
+        <v>884</v>
+      </c>
+      <c r="B227" s="9" t="s">
+        <v>885</v>
+      </c>
+      <c r="C227" s="9">
+        <v>2022</v>
+      </c>
+      <c r="D227" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="E227" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F227" s="9" t="s">
+        <v>875</v>
+      </c>
+      <c r="G227" s="9" t="s">
+        <v>886</v>
+      </c>
+      <c r="H227" s="9" t="s">
+        <v>917</v>
+      </c>
+      <c r="I227" s="9">
+        <v>4</v>
+      </c>
+      <c r="J227" s="9">
+        <v>5</v>
+      </c>
+      <c r="K227" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="L227" s="6" t="s">
+        <v>921</v>
+      </c>
+      <c r="M227" s="9" t="s">
+        <v>919</v>
+      </c>
+      <c r="N227" s="9" t="s">
+        <v>890</v>
+      </c>
+      <c r="O227" s="9" t="s">
+        <v>891</v>
+      </c>
+      <c r="P227" s="9" t="s">
+        <v>892</v>
+      </c>
+      <c r="Q227" s="9" t="s">
+        <v>893</v>
+      </c>
+      <c r="R227" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="S227" s="9">
+        <v>1</v>
+      </c>
+      <c r="T227" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="U227" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="V227" s="9">
+        <v>-0.17</v>
+      </c>
+      <c r="W227" s="9" t="s">
+        <v>920</v>
+      </c>
+      <c r="X227" s="9">
+        <v>-0.3</v>
+      </c>
+      <c r="Y227" s="9">
+        <v>-0.04</v>
+      </c>
+      <c r="Z227" s="9">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A228" s="9"/>
+      <c r="B228" s="9"/>
+      <c r="C228" s="9"/>
+      <c r="D228" s="9"/>
+      <c r="E228" s="9"/>
+      <c r="F228" s="9"/>
+      <c r="G228" s="9"/>
+      <c r="H228" s="9"/>
+      <c r="I228" s="9"/>
+      <c r="J228" s="9"/>
+      <c r="K228" s="9"/>
+      <c r="L228" s="5"/>
+      <c r="M228" s="9"/>
+      <c r="N228" s="9"/>
+      <c r="O228" s="9"/>
+      <c r="P228" s="9"/>
+      <c r="Q228" s="9"/>
+      <c r="R228" s="9"/>
+      <c r="S228" s="9"/>
+      <c r="T228" s="9"/>
+      <c r="U228" s="9"/>
+      <c r="V228" s="9"/>
+      <c r="W228" s="9"/>
+      <c r="X228" s="9"/>
+      <c r="Y228" s="9"/>
+      <c r="Z228" s="9"/>
+    </row>
+    <row r="229" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A229" s="9"/>
+      <c r="B229" s="9"/>
+      <c r="C229" s="9"/>
+      <c r="D229" s="9"/>
+      <c r="E229" s="9"/>
+      <c r="F229" s="9"/>
+      <c r="G229" s="9"/>
+      <c r="H229" s="9"/>
+      <c r="I229" s="9"/>
+      <c r="J229" s="9"/>
+      <c r="K229" s="9"/>
+      <c r="L229" s="6" t="s">
+        <v>922</v>
+      </c>
+      <c r="M229" s="9"/>
+      <c r="N229" s="9"/>
+      <c r="O229" s="9"/>
+      <c r="P229" s="9"/>
+      <c r="Q229" s="9"/>
+      <c r="R229" s="9"/>
+      <c r="S229" s="9"/>
+      <c r="T229" s="9"/>
+      <c r="U229" s="9"/>
+      <c r="V229" s="9"/>
+      <c r="W229" s="9"/>
+      <c r="X229" s="9"/>
+      <c r="Y229" s="9"/>
+      <c r="Z229" s="9"/>
+    </row>
+    <row r="230" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A230" s="9"/>
+      <c r="B230" s="9"/>
+      <c r="C230" s="9"/>
+      <c r="D230" s="9"/>
+      <c r="E230" s="9"/>
+      <c r="F230" s="9"/>
+      <c r="G230" s="9"/>
+      <c r="H230" s="9"/>
+      <c r="I230" s="9"/>
+      <c r="J230" s="9"/>
+      <c r="K230" s="9"/>
+      <c r="L230" s="5"/>
+      <c r="M230" s="9"/>
+      <c r="N230" s="9"/>
+      <c r="O230" s="9"/>
+      <c r="P230" s="9"/>
+      <c r="Q230" s="9"/>
+      <c r="R230" s="9"/>
+      <c r="S230" s="9"/>
+      <c r="T230" s="9"/>
+      <c r="U230" s="9"/>
+      <c r="V230" s="9"/>
+      <c r="W230" s="9"/>
+      <c r="X230" s="9"/>
+      <c r="Y230" s="9"/>
+      <c r="Z230" s="9"/>
+    </row>
+    <row r="231" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A231" s="9"/>
+      <c r="B231" s="9"/>
+      <c r="C231" s="9"/>
+      <c r="D231" s="9"/>
+      <c r="E231" s="9"/>
+      <c r="F231" s="9"/>
+      <c r="G231" s="9"/>
+      <c r="H231" s="9"/>
+      <c r="I231" s="9"/>
+      <c r="J231" s="9"/>
+      <c r="K231" s="9"/>
+      <c r="L231" s="6" t="s">
+        <v>923</v>
+      </c>
+      <c r="M231" s="9"/>
+      <c r="N231" s="9"/>
+      <c r="O231" s="9"/>
+      <c r="P231" s="9"/>
+      <c r="Q231" s="9"/>
+      <c r="R231" s="9"/>
+      <c r="S231" s="9"/>
+      <c r="T231" s="9"/>
+      <c r="U231" s="9"/>
+      <c r="V231" s="9"/>
+      <c r="W231" s="9"/>
+      <c r="X231" s="9"/>
+      <c r="Y231" s="9"/>
+      <c r="Z231" s="9"/>
+    </row>
+    <row r="232" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A232" s="9"/>
+      <c r="B232" s="9"/>
+      <c r="C232" s="9"/>
+      <c r="D232" s="9"/>
+      <c r="E232" s="9"/>
+      <c r="F232" s="9"/>
+      <c r="G232" s="9"/>
+      <c r="H232" s="9"/>
+      <c r="I232" s="9"/>
+      <c r="J232" s="9"/>
+      <c r="K232" s="9"/>
+      <c r="L232" s="5"/>
+      <c r="M232" s="9"/>
+      <c r="N232" s="9"/>
+      <c r="O232" s="9"/>
+      <c r="P232" s="9"/>
+      <c r="Q232" s="9"/>
+      <c r="R232" s="9"/>
+      <c r="S232" s="9"/>
+      <c r="T232" s="9"/>
+      <c r="U232" s="9"/>
+      <c r="V232" s="9"/>
+      <c r="W232" s="9"/>
+      <c r="X232" s="9"/>
+      <c r="Y232" s="9"/>
+      <c r="Z232" s="9"/>
+    </row>
+    <row r="233" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A233" s="9"/>
+      <c r="B233" s="9"/>
+      <c r="C233" s="9"/>
+      <c r="D233" s="9"/>
+      <c r="E233" s="9"/>
+      <c r="F233" s="9"/>
+      <c r="G233" s="9"/>
+      <c r="H233" s="9"/>
+      <c r="I233" s="9"/>
+      <c r="J233" s="9"/>
+      <c r="K233" s="9"/>
+      <c r="L233" s="6" t="s">
+        <v>900</v>
+      </c>
+      <c r="M233" s="9"/>
+      <c r="N233" s="9"/>
+      <c r="O233" s="9"/>
+      <c r="P233" s="9"/>
+      <c r="Q233" s="9"/>
+      <c r="R233" s="9"/>
+      <c r="S233" s="9"/>
+      <c r="T233" s="9"/>
+      <c r="U233" s="9"/>
+      <c r="V233" s="9"/>
+      <c r="W233" s="9"/>
+      <c r="X233" s="9"/>
+      <c r="Y233" s="9"/>
+      <c r="Z233" s="9"/>
+    </row>
+    <row r="234" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A234" s="9"/>
+      <c r="B234" s="9"/>
+      <c r="C234" s="9"/>
+      <c r="D234" s="9"/>
+      <c r="E234" s="9"/>
+      <c r="F234" s="9"/>
+      <c r="G234" s="9"/>
+      <c r="H234" s="9"/>
+      <c r="I234" s="9"/>
+      <c r="J234" s="9"/>
+      <c r="K234" s="9"/>
+      <c r="L234" s="5"/>
+      <c r="M234" s="9"/>
+      <c r="N234" s="9"/>
+      <c r="O234" s="9"/>
+      <c r="P234" s="9"/>
+      <c r="Q234" s="9"/>
+      <c r="R234" s="9"/>
+      <c r="S234" s="9"/>
+      <c r="T234" s="9"/>
+      <c r="U234" s="9"/>
+      <c r="V234" s="9"/>
+      <c r="W234" s="9"/>
+      <c r="X234" s="9"/>
+      <c r="Y234" s="9"/>
+      <c r="Z234" s="9"/>
+    </row>
+    <row r="235" spans="1:26" ht="27.4" x14ac:dyDescent="0.6">
+      <c r="A235" s="9"/>
+      <c r="B235" s="9"/>
+      <c r="C235" s="9"/>
+      <c r="D235" s="9"/>
+      <c r="E235" s="9"/>
+      <c r="F235" s="9"/>
+      <c r="G235" s="9"/>
+      <c r="H235" s="9"/>
+      <c r="I235" s="9"/>
+      <c r="J235" s="9"/>
+      <c r="K235" s="9"/>
+      <c r="L235" s="6" t="s">
+        <v>924</v>
+      </c>
+      <c r="M235" s="9"/>
+      <c r="N235" s="9"/>
+      <c r="O235" s="9"/>
+      <c r="P235" s="9"/>
+      <c r="Q235" s="9"/>
+      <c r="R235" s="9"/>
+      <c r="S235" s="9"/>
+      <c r="T235" s="9"/>
+      <c r="U235" s="9"/>
+      <c r="V235" s="9"/>
+      <c r="W235" s="9"/>
+      <c r="X235" s="9"/>
+      <c r="Y235" s="9"/>
+      <c r="Z235" s="9"/>
+    </row>
+    <row r="236" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A236" s="9"/>
+      <c r="B236" s="9"/>
+      <c r="C236" s="9"/>
+      <c r="D236" s="9"/>
+      <c r="E236" s="9"/>
+      <c r="F236" s="9"/>
+      <c r="G236" s="9"/>
+      <c r="H236" s="9"/>
+      <c r="I236" s="9"/>
+      <c r="J236" s="9"/>
+      <c r="K236" s="9"/>
+      <c r="L236" s="5"/>
+      <c r="M236" s="9"/>
+      <c r="N236" s="9"/>
+      <c r="O236" s="9"/>
+      <c r="P236" s="9"/>
+      <c r="Q236" s="9"/>
+      <c r="R236" s="9"/>
+      <c r="S236" s="9"/>
+      <c r="T236" s="9"/>
+      <c r="U236" s="9"/>
+      <c r="V236" s="9"/>
+      <c r="W236" s="9"/>
+      <c r="X236" s="9"/>
+      <c r="Y236" s="9"/>
+      <c r="Z236" s="9"/>
+    </row>
+    <row r="237" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A237" s="9"/>
+      <c r="B237" s="9"/>
+      <c r="C237" s="9"/>
+      <c r="D237" s="9"/>
+      <c r="E237" s="9"/>
+      <c r="F237" s="9"/>
+      <c r="G237" s="9"/>
+      <c r="H237" s="9"/>
+      <c r="I237" s="9"/>
+      <c r="J237" s="9"/>
+      <c r="K237" s="9"/>
+      <c r="L237" s="5"/>
+      <c r="M237" s="9"/>
+      <c r="N237" s="9"/>
+      <c r="O237" s="9"/>
+      <c r="P237" s="9"/>
+      <c r="Q237" s="9"/>
+      <c r="R237" s="9"/>
+      <c r="S237" s="9"/>
+      <c r="T237" s="9"/>
+      <c r="U237" s="9"/>
+      <c r="V237" s="9"/>
+      <c r="W237" s="9"/>
+      <c r="X237" s="9"/>
+      <c r="Y237" s="9"/>
+      <c r="Z237" s="9"/>
+    </row>
+    <row r="238" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A238" s="9"/>
+      <c r="B238" s="9"/>
+      <c r="C238" s="9"/>
+      <c r="D238" s="9"/>
+      <c r="E238" s="9"/>
+      <c r="F238" s="9"/>
+      <c r="G238" s="9"/>
+      <c r="H238" s="9"/>
+      <c r="I238" s="9"/>
+      <c r="J238" s="9"/>
+      <c r="K238" s="9"/>
+      <c r="L238" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="M238" s="9"/>
+      <c r="N238" s="9"/>
+      <c r="O238" s="9"/>
+      <c r="P238" s="9"/>
+      <c r="Q238" s="9"/>
+      <c r="R238" s="9"/>
+      <c r="S238" s="9"/>
+      <c r="T238" s="9"/>
+      <c r="U238" s="9"/>
+      <c r="V238" s="9"/>
+      <c r="W238" s="9"/>
+      <c r="X238" s="9"/>
+      <c r="Y238" s="9"/>
+      <c r="Z238" s="9"/>
+    </row>
+    <row r="239" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A239" s="9"/>
+      <c r="B239" s="9"/>
+      <c r="C239" s="9"/>
+      <c r="D239" s="9"/>
+      <c r="E239" s="9"/>
+      <c r="F239" s="9"/>
+      <c r="G239" s="9"/>
+      <c r="H239" s="9"/>
+      <c r="I239" s="9"/>
+      <c r="J239" s="9"/>
+      <c r="K239" s="9"/>
+      <c r="L239" s="5"/>
+      <c r="M239" s="9"/>
+      <c r="N239" s="9"/>
+      <c r="O239" s="9"/>
+      <c r="P239" s="9"/>
+      <c r="Q239" s="9"/>
+      <c r="R239" s="9"/>
+      <c r="S239" s="9"/>
+      <c r="T239" s="9"/>
+      <c r="U239" s="9"/>
+      <c r="V239" s="9"/>
+      <c r="W239" s="9"/>
+      <c r="X239" s="9"/>
+      <c r="Y239" s="9"/>
+      <c r="Z239" s="9"/>
+    </row>
+    <row r="240" spans="1:26" x14ac:dyDescent="0.6">
+      <c r="A240" s="9"/>
+      <c r="B240" s="9"/>
+      <c r="C240" s="9"/>
+      <c r="D240" s="9"/>
+      <c r="E240" s="9"/>
+      <c r="F240" s="9"/>
+      <c r="G240" s="9"/>
+      <c r="H240" s="9"/>
+      <c r="I240" s="9"/>
+      <c r="J240" s="9"/>
+      <c r="K240" s="9"/>
+      <c r="L240" s="6" t="s">
+        <v>926</v>
+      </c>
+      <c r="M240" s="9"/>
+      <c r="N240" s="9"/>
+      <c r="O240" s="9"/>
+      <c r="P240" s="9"/>
+      <c r="Q240" s="9"/>
+      <c r="R240" s="9"/>
+      <c r="S240" s="9"/>
+      <c r="T240" s="9"/>
+      <c r="U240" s="9"/>
+      <c r="V240" s="9"/>
+      <c r="W240" s="9"/>
+      <c r="X240" s="9"/>
+      <c r="Y240" s="9"/>
+      <c r="Z240" s="9"/>
+    </row>
+    <row r="241" spans="1:26" ht="40.5" x14ac:dyDescent="0.6">
+      <c r="A241" s="7" t="s">
+        <v>884</v>
+      </c>
+      <c r="B241" s="7" t="s">
+        <v>885</v>
+      </c>
+      <c r="C241" s="7">
+        <v>2022</v>
+      </c>
+      <c r="D241" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E241" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F241" s="7" t="s">
+        <v>882</v>
+      </c>
+      <c r="G241" s="7" t="s">
+        <v>886</v>
+      </c>
+      <c r="H241" s="7" t="s">
+        <v>917</v>
+      </c>
+      <c r="I241" s="7">
+        <v>4</v>
+      </c>
+      <c r="J241" s="7">
+        <v>5</v>
+      </c>
+      <c r="K241" s="7" t="s">
+        <v>870</v>
+      </c>
+      <c r="L241" s="7" t="s">
+        <v>927</v>
+      </c>
+      <c r="M241" s="7" t="s">
+        <v>919</v>
+      </c>
+      <c r="N241" s="7" t="s">
+        <v>890</v>
+      </c>
+      <c r="O241" s="7" t="s">
+        <v>891</v>
+      </c>
+      <c r="P241" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="Q241" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="R241" s="7" t="s">
+        <v>909</v>
+      </c>
+      <c r="S241" s="7">
+        <v>1</v>
+      </c>
+      <c r="T241" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="U241" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="V241" s="7">
+        <v>-0.17</v>
+      </c>
+      <c r="W241" s="7" t="s">
+        <v>920</v>
+      </c>
+      <c r="X241" s="7"/>
+      <c r="Y241" s="7"/>
+      <c r="Z241" s="7">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="150">
+    <mergeCell ref="W227:W240"/>
+    <mergeCell ref="X227:X240"/>
+    <mergeCell ref="Y227:Y240"/>
+    <mergeCell ref="Z227:Z240"/>
+    <mergeCell ref="Q227:Q240"/>
+    <mergeCell ref="R227:R240"/>
+    <mergeCell ref="S227:S240"/>
+    <mergeCell ref="T227:T240"/>
+    <mergeCell ref="U227:U240"/>
+    <mergeCell ref="V227:V240"/>
+    <mergeCell ref="J227:J240"/>
+    <mergeCell ref="K227:K240"/>
+    <mergeCell ref="M227:M240"/>
+    <mergeCell ref="N227:N240"/>
+    <mergeCell ref="O227:O240"/>
+    <mergeCell ref="P227:P240"/>
+    <mergeCell ref="Z211:Z224"/>
+    <mergeCell ref="A227:A240"/>
+    <mergeCell ref="B227:B240"/>
+    <mergeCell ref="C227:C240"/>
+    <mergeCell ref="D227:D240"/>
+    <mergeCell ref="E227:E240"/>
+    <mergeCell ref="F227:F240"/>
+    <mergeCell ref="G227:G240"/>
+    <mergeCell ref="H227:H240"/>
+    <mergeCell ref="I227:I240"/>
+    <mergeCell ref="T211:T224"/>
+    <mergeCell ref="U211:U224"/>
+    <mergeCell ref="V211:V224"/>
+    <mergeCell ref="W211:W224"/>
+    <mergeCell ref="X211:X224"/>
+    <mergeCell ref="Y211:Y224"/>
+    <mergeCell ref="N211:N224"/>
+    <mergeCell ref="O211:O224"/>
+    <mergeCell ref="P211:P224"/>
+    <mergeCell ref="Q211:Q224"/>
+    <mergeCell ref="R211:R224"/>
+    <mergeCell ref="S211:S224"/>
+    <mergeCell ref="G211:G224"/>
+    <mergeCell ref="H211:H224"/>
+    <mergeCell ref="I211:I224"/>
+    <mergeCell ref="J211:J224"/>
+    <mergeCell ref="K211:K224"/>
+    <mergeCell ref="M211:M224"/>
+    <mergeCell ref="W195:W208"/>
+    <mergeCell ref="X195:X208"/>
+    <mergeCell ref="Y195:Y208"/>
+    <mergeCell ref="Z195:Z208"/>
+    <mergeCell ref="A211:A224"/>
+    <mergeCell ref="B211:B224"/>
+    <mergeCell ref="C211:C224"/>
+    <mergeCell ref="D211:D224"/>
+    <mergeCell ref="E211:E224"/>
+    <mergeCell ref="F211:F224"/>
+    <mergeCell ref="Q195:Q208"/>
+    <mergeCell ref="R195:R208"/>
+    <mergeCell ref="S195:S208"/>
+    <mergeCell ref="T195:T208"/>
+    <mergeCell ref="U195:U208"/>
+    <mergeCell ref="V195:V208"/>
+    <mergeCell ref="J195:J208"/>
+    <mergeCell ref="K195:K208"/>
+    <mergeCell ref="M195:M208"/>
+    <mergeCell ref="N195:N208"/>
+    <mergeCell ref="O195:O208"/>
+    <mergeCell ref="P195:P208"/>
+    <mergeCell ref="Z176:Z191"/>
+    <mergeCell ref="A195:A208"/>
+    <mergeCell ref="B195:B208"/>
+    <mergeCell ref="C195:C208"/>
+    <mergeCell ref="D195:D208"/>
+    <mergeCell ref="E195:E208"/>
+    <mergeCell ref="F195:F208"/>
+    <mergeCell ref="G195:G208"/>
+    <mergeCell ref="H195:H208"/>
+    <mergeCell ref="I195:I208"/>
+    <mergeCell ref="T176:T191"/>
+    <mergeCell ref="U176:U191"/>
+    <mergeCell ref="V176:V191"/>
+    <mergeCell ref="W176:W191"/>
+    <mergeCell ref="X176:X191"/>
+    <mergeCell ref="Y176:Y191"/>
+    <mergeCell ref="N176:N191"/>
+    <mergeCell ref="O176:O191"/>
+    <mergeCell ref="P176:P191"/>
+    <mergeCell ref="Q176:Q191"/>
+    <mergeCell ref="R176:R191"/>
+    <mergeCell ref="S176:S191"/>
+    <mergeCell ref="G176:G191"/>
+    <mergeCell ref="H176:H191"/>
+    <mergeCell ref="I176:I191"/>
+    <mergeCell ref="J176:J191"/>
+    <mergeCell ref="K176:K191"/>
+    <mergeCell ref="M176:M191"/>
+    <mergeCell ref="W158:W173"/>
+    <mergeCell ref="X158:X173"/>
+    <mergeCell ref="Y158:Y173"/>
+    <mergeCell ref="Z158:Z173"/>
+    <mergeCell ref="A176:A191"/>
+    <mergeCell ref="B176:B191"/>
+    <mergeCell ref="C176:C191"/>
+    <mergeCell ref="D176:D191"/>
+    <mergeCell ref="E176:E191"/>
+    <mergeCell ref="F176:F191"/>
+    <mergeCell ref="Q158:Q173"/>
+    <mergeCell ref="R158:R173"/>
+    <mergeCell ref="S158:S173"/>
+    <mergeCell ref="T158:T173"/>
+    <mergeCell ref="U158:U173"/>
+    <mergeCell ref="V158:V173"/>
+    <mergeCell ref="J158:J173"/>
+    <mergeCell ref="K158:K173"/>
+    <mergeCell ref="M158:M173"/>
+    <mergeCell ref="N158:N173"/>
+    <mergeCell ref="O158:O173"/>
+    <mergeCell ref="P158:P173"/>
+    <mergeCell ref="Z140:Z155"/>
+    <mergeCell ref="A158:A173"/>
+    <mergeCell ref="B158:B173"/>
+    <mergeCell ref="C158:C173"/>
+    <mergeCell ref="D158:D173"/>
+    <mergeCell ref="E158:E173"/>
+    <mergeCell ref="F158:F173"/>
+    <mergeCell ref="G158:G173"/>
+    <mergeCell ref="H158:H173"/>
+    <mergeCell ref="I158:I173"/>
+    <mergeCell ref="T140:T155"/>
+    <mergeCell ref="U140:U155"/>
+    <mergeCell ref="V140:V155"/>
+    <mergeCell ref="W140:W155"/>
+    <mergeCell ref="X140:X155"/>
+    <mergeCell ref="Y140:Y155"/>
+    <mergeCell ref="N140:N155"/>
+    <mergeCell ref="O140:O155"/>
+    <mergeCell ref="P140:P155"/>
+    <mergeCell ref="Q140:Q155"/>
+    <mergeCell ref="R140:R155"/>
+    <mergeCell ref="S140:S155"/>
+    <mergeCell ref="G140:G155"/>
+    <mergeCell ref="H140:H155"/>
+    <mergeCell ref="I140:I155"/>
+    <mergeCell ref="J140:J155"/>
+    <mergeCell ref="K140:K155"/>
+    <mergeCell ref="M140:M155"/>
+    <mergeCell ref="A140:A155"/>
+    <mergeCell ref="B140:B155"/>
+    <mergeCell ref="C140:C155"/>
+    <mergeCell ref="D140:D155"/>
+    <mergeCell ref="E140:E155"/>
+    <mergeCell ref="F140:F155"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
